--- a/database/event/2110/event_2110_evp_summary.xlsx
+++ b/database/event/2110/event_2110_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.1866</v>
+        <v>7.392</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4219</v>
+        <v>1.4626</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4819</v>
+        <v>2.5011</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1866</v>
+        <v>7.392</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4636</v>
+        <v>3.669</v>
       </c>
       <c r="G2" t="n">
         <v>3.723</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4636</v>
+        <v>3.669</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8073</v>
+        <v>2.9738</v>
       </c>
       <c r="J2" t="n">
         <v>3.723</v>
@@ -529,7 +529,7 @@
         <v>128</v>
       </c>
       <c r="M2" t="n">
-        <v>6.5303</v>
+        <v>6.6968</v>
       </c>
       <c r="N2" t="n">
         <v>245</v>
@@ -548,7 +548,7 @@
         <v>1.3899</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4164</v>
+        <v>2.3547</v>
       </c>
       <c r="E3" t="n">
         <v>7.0245</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.2689</v>
+        <v>4.2804</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8446</v>
+        <v>0.8469</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3032</v>
+        <v>1.2614</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2689</v>
+        <v>4.2804</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1113</v>
+        <v>4.1228</v>
       </c>
       <c r="G4" t="n">
         <v>0.1576</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1113</v>
+        <v>4.1228</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3324</v>
+        <v>3.3416</v>
       </c>
       <c r="J4" t="n">
         <v>0.1576</v>
@@ -621,7 +621,7 @@
         <v>78</v>
       </c>
       <c r="M4" t="n">
-        <v>3.49</v>
+        <v>3.4992</v>
       </c>
       <c r="N4" t="n">
         <v>234</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.714</v>
+        <v>3.9144</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7348</v>
+        <v>0.7745</v>
       </c>
       <c r="D5" t="n">
-        <v>1.079</v>
+        <v>1.1156</v>
       </c>
       <c r="E5" t="n">
-        <v>3.714</v>
+        <v>3.9144</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1662</v>
+        <v>3.3666</v>
       </c>
       <c r="G5" t="n">
         <v>0.5478</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1662</v>
+        <v>3.3666</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5663</v>
+        <v>2.7287</v>
       </c>
       <c r="J5" t="n">
         <v>0.5478</v>
@@ -667,7 +667,7 @@
         <v>78</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1141</v>
+        <v>3.2765</v>
       </c>
       <c r="N5" t="n">
         <v>234</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.3139</v>
+        <v>3.6714</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.7264</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9174</v>
+        <v>1.0188</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3139</v>
+        <v>3.6714</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0921</v>
+        <v>2.4496</v>
       </c>
       <c r="G6" t="n">
         <v>1.2218</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0921</v>
+        <v>2.4496</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6957</v>
+        <v>1.9855</v>
       </c>
       <c r="J6" t="n">
         <v>1.2218</v>
@@ -713,7 +713,7 @@
         <v>132</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9175</v>
+        <v>3.2073</v>
       </c>
       <c r="N6" t="n">
         <v>186</v>
@@ -722,139 +722,139 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8522</v>
+        <v>2.8942</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5643</v>
+        <v>0.5726</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7309</v>
+        <v>0.7091</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8522</v>
+        <v>2.8942</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8522</v>
+        <v>1.8851</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1.0091</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8522</v>
+        <v>1.8851</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8655</v>
+        <v>1.5279</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.0091</v>
       </c>
       <c r="K7" t="n">
-        <v>200</v>
+        <v>53</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8655</v>
+        <v>2.537</v>
       </c>
       <c r="N7" t="n">
-        <v>200</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7268</v>
+        <v>2.8783</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5395</v>
+        <v>0.5695</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6802</v>
+        <v>0.7028</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7268</v>
+        <v>2.8783</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7177</v>
+        <v>1.7829</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0091</v>
+        <v>1.0954</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7177</v>
+        <v>1.7829</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3922</v>
+        <v>1.4451</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0091</v>
+        <v>1.0954</v>
       </c>
       <c r="K8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L8" t="n">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4013</v>
+        <v>2.5405</v>
       </c>
       <c r="N8" t="n">
-        <v>127</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5898</v>
+        <v>2.8416</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5124</v>
+        <v>0.5622</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6249</v>
+        <v>0.6882</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5898</v>
+        <v>2.8416</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4944</v>
+        <v>2.8416</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0954</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4944</v>
+        <v>2.8416</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2112</v>
+        <v>2.8655</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0954</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>54</v>
+        <v>200</v>
       </c>
       <c r="L9" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3066</v>
+        <v>2.8655</v>
       </c>
       <c r="N9" t="n">
-        <v>186</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5746</v>
+        <v>2.565</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5094</v>
+        <v>0.5075</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6187</v>
+        <v>0.578</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5746</v>
+        <v>2.565</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5746</v>
+        <v>2.565</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5746</v>
+        <v>2.565</v>
       </c>
       <c r="I10" t="n">
         <v>2.5866</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8062</v>
+        <v>1.7995</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3574</v>
+        <v>0.356</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3083</v>
+        <v>0.273</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8062</v>
+        <v>1.7995</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8062</v>
+        <v>1.7995</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8062</v>
+        <v>1.7995</v>
       </c>
       <c r="I11" t="n">
         <v>1.8146</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7807</v>
+        <v>1.7741</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3523</v>
+        <v>0.351</v>
       </c>
       <c r="D12" t="n">
-        <v>0.298</v>
+        <v>0.2629</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7807</v>
+        <v>1.7741</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7807</v>
+        <v>1.7741</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7807</v>
+        <v>1.7741</v>
       </c>
       <c r="I12" t="n">
         <v>1.789</v>
@@ -1008,7 +1008,7 @@
         <v>0.3324</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2574</v>
+        <v>0.2255</v>
       </c>
       <c r="E13" t="n">
         <v>1.6802</v>
@@ -1044,216 +1044,216 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4745</v>
+        <v>1.5524</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2917</v>
+        <v>0.3072</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1743</v>
+        <v>0.1746</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4745</v>
+        <v>1.5524</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5191</v>
+        <v>1.8843</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9554</v>
+        <v>-0.3319</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5191</v>
+        <v>1.8843</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4208</v>
+        <v>1.5273</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9554</v>
+        <v>-0.3319</v>
       </c>
       <c r="K14" t="n">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="L14" t="n">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3762</v>
+        <v>1.1954</v>
       </c>
       <c r="N14" t="n">
-        <v>245</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>znajder</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.375</v>
+        <v>1.5428</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2721</v>
+        <v>0.3053</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1341</v>
+        <v>0.1707</v>
       </c>
       <c r="E15" t="n">
-        <v>1.375</v>
+        <v>1.5428</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7916</v>
+        <v>0.5874</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5834</v>
+        <v>0.9554</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7916</v>
+        <v>0.5874</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.4761</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5834</v>
+        <v>0.9554</v>
       </c>
       <c r="K15" t="n">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="L15" t="n">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="M15" t="n">
-        <v>1.225</v>
+        <v>1.4315</v>
       </c>
       <c r="N15" t="n">
-        <v>127</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>znajder</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3319</v>
+        <v>1.375</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2635</v>
+        <v>0.2721</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1167</v>
+        <v>0.1039</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3319</v>
+        <v>1.375</v>
       </c>
       <c r="F16" t="n">
-        <v>0.957</v>
+        <v>0.7916</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3749</v>
+        <v>0.5834</v>
       </c>
       <c r="H16" t="n">
-        <v>0.957</v>
+        <v>0.7916</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3749</v>
+        <v>0.5834</v>
       </c>
       <c r="K16" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L16" t="n">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1506</v>
+        <v>1.225</v>
       </c>
       <c r="N16" t="n">
-        <v>186</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2705</v>
+        <v>1.3319</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2514</v>
+        <v>0.2635</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0919</v>
+        <v>0.0867</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2705</v>
+        <v>1.3319</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2705</v>
+        <v>0.957</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.3749</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2705</v>
+        <v>0.957</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2705</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.3749</v>
       </c>
       <c r="K17" t="n">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2705</v>
+        <v>1.1506</v>
       </c>
       <c r="N17" t="n">
-        <v>131</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1707</v>
+        <v>1.2705</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2316</v>
+        <v>0.2514</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0516</v>
+        <v>0.0623</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1707</v>
+        <v>1.2705</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1707</v>
+        <v>1.2705</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1707</v>
+        <v>1.2705</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1707</v>
+        <v>1.2705</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1707</v>
+        <v>1.2705</v>
       </c>
       <c r="N18" t="n">
         <v>131</v>
@@ -1274,47 +1274,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1628</v>
+        <v>1.1707</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2301</v>
+        <v>0.2316</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0484</v>
+        <v>0.0225</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1628</v>
+        <v>1.1707</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4947</v>
+        <v>1.1707</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3319</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4947</v>
+        <v>1.1707</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2115</v>
+        <v>1.1707</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3319</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="L19" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8796</v>
+        <v>1.1707</v>
       </c>
       <c r="N19" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20">
@@ -1330,7 +1330,7 @@
         <v>0.2188</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0254</v>
+        <v>-0.0033</v>
       </c>
       <c r="E20" t="n">
         <v>1.106</v>
@@ -1376,7 +1376,7 @@
         <v>0.1351</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1454</v>
+        <v>-0.1718</v>
       </c>
       <c r="E21" t="n">
         <v>0.6830000000000001</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6413</v>
+        <v>0.6389</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1269</v>
+        <v>0.1264</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1623</v>
+        <v>-0.1894</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6413</v>
+        <v>0.6389</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6413</v>
+        <v>0.6389</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6413</v>
+        <v>0.6389</v>
       </c>
       <c r="I22" t="n">
         <v>0.6443</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5433</v>
+        <v>0.6072</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1075</v>
+        <v>0.1201</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2019</v>
+        <v>-0.202</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5433</v>
+        <v>0.6072</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5433</v>
+        <v>1.6072</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5433</v>
+        <v>1.6072</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5433</v>
+        <v>1.3027</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K23" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5433</v>
+        <v>0.3027</v>
       </c>
       <c r="N23" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4576</v>
+        <v>0.5433</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0905</v>
+        <v>0.1075</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2365</v>
+        <v>-0.2275</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4576</v>
+        <v>0.5433</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4576</v>
+        <v>0.5433</v>
       </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4576</v>
+        <v>0.5433</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1814</v>
+        <v>0.5433</v>
       </c>
       <c r="J24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="L24" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1814</v>
+        <v>0.5433</v>
       </c>
       <c r="N24" t="n">
-        <v>127</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25">
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2998</v>
+        <v>0.2986</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0593</v>
+        <v>0.0591</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3002</v>
+        <v>-0.3249</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2998</v>
+        <v>0.2986</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2998</v>
+        <v>0.2986</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2998</v>
+        <v>0.2986</v>
       </c>
       <c r="I25" t="n">
         <v>0.3012</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2202</v>
+        <v>0.2194</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0436</v>
+        <v>0.0434</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3324</v>
+        <v>-0.3565</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2202</v>
+        <v>0.2194</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2202</v>
+        <v>0.2194</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2202</v>
+        <v>0.2194</v>
       </c>
       <c r="I26" t="n">
         <v>0.2212</v>
@@ -1652,7 +1652,7 @@
         <v>0.0385</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3428</v>
+        <v>-0.3665</v>
       </c>
       <c r="E27" t="n">
         <v>0.1944</v>
@@ -1698,7 +1698,7 @@
         <v>0.0283</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3635</v>
+        <v>-0.3869</v>
       </c>
       <c r="E28" t="n">
         <v>0.1432</v>
@@ -1744,7 +1744,7 @@
         <v>0.0254</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3694</v>
+        <v>-0.3927</v>
       </c>
       <c r="E29" t="n">
         <v>0.1286</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0506</v>
+        <v>0.0504</v>
       </c>
       <c r="C30" t="n">
         <v>0.01</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4009</v>
+        <v>-0.4238</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0506</v>
+        <v>0.0504</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0506</v>
+        <v>0.0504</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0506</v>
+        <v>0.0504</v>
       </c>
       <c r="I30" t="n">
         <v>0.0508</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0776</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0154</v>
+        <v>-0.0153</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4527</v>
+        <v>-0.4747</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0776</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0776</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0776</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="I31" t="n">
         <v>-0.078</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0216</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4655</v>
+        <v>-0.4875</v>
       </c>
       <c r="E32" t="n">
         <v>-0.1093</v>
@@ -1928,7 +1928,7 @@
         <v>-0.0333</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.4893</v>
+        <v>-0.5109</v>
       </c>
       <c r="E33" t="n">
         <v>-0.1682</v>
@@ -1974,7 +1974,7 @@
         <v>-0.0425</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5082</v>
+        <v>-0.5295</v>
       </c>
       <c r="E34" t="n">
         <v>-0.2149</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8097</v>
+        <v>-0.6723</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1602</v>
+        <v>-0.133</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-0.7118</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8097</v>
+        <v>-0.6723</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2654</v>
+        <v>0.4028</v>
       </c>
       <c r="G35" t="n">
         <v>-1.0751</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2654</v>
+        <v>0.4028</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2151</v>
+        <v>0.3265</v>
       </c>
       <c r="J35" t="n">
         <v>-1.0751</v>
@@ -2047,7 +2047,7 @@
         <v>132</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.7485999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>186</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1792</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7873</v>
+        <v>-0.8048</v>
       </c>
       <c r="E36" t="n">
         <v>-0.9058</v>
@@ -2112,7 +2112,7 @@
         <v>-0.1864</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8018999999999999</v>
+        <v>-0.8192</v>
       </c>
       <c r="E37" t="n">
         <v>-0.9421</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3046</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0432</v>
+        <v>-1.0572</v>
       </c>
       <c r="E38" t="n">
         <v>-1.5393</v>
@@ -2204,7 +2204,7 @@
         <v>-0.3365</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1085</v>
+        <v>-1.1215</v>
       </c>
       <c r="E39" t="n">
         <v>-1.7009</v>
@@ -2250,7 +2250,7 @@
         <v>-0.4822</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4058</v>
+        <v>-1.4148</v>
       </c>
       <c r="E40" t="n">
         <v>-2.4369</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.6675</v>
+        <v>-2.6575</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5278</v>
+        <v>-0.5258</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.499</v>
+        <v>-1.5027</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.6675</v>
+        <v>-2.6575</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.6675</v>
+        <v>-2.6575</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.6675</v>
+        <v>-2.6575</v>
       </c>
       <c r="I41" t="n">
         <v>-2.6799</v>

--- a/database/event/2110/event_2110_evp_summary.xlsx
+++ b/database/event/2110/event_2110_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.392</v>
+        <v>6.6535</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4626</v>
+        <v>1.3164</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5011</v>
+        <v>2.3657</v>
       </c>
       <c r="E2" t="n">
-        <v>7.392</v>
+        <v>6.6535</v>
       </c>
       <c r="F2" t="n">
-        <v>3.669</v>
+        <v>2.7285</v>
       </c>
       <c r="G2" t="n">
-        <v>3.723</v>
+        <v>3.925</v>
       </c>
       <c r="H2" t="n">
-        <v>3.669</v>
+        <v>4.1271</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9738</v>
+        <v>2.1459</v>
       </c>
       <c r="J2" t="n">
-        <v>3.723</v>
+        <v>3.925</v>
       </c>
       <c r="K2" t="n">
         <v>117</v>
@@ -529,7 +529,7 @@
         <v>128</v>
       </c>
       <c r="M2" t="n">
-        <v>6.6968</v>
+        <v>6.0709</v>
       </c>
       <c r="N2" t="n">
         <v>245</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.0245</v>
+        <v>6.6232</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3899</v>
+        <v>1.3105</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3547</v>
+        <v>2.352</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0245</v>
+        <v>6.6232</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4678</v>
+        <v>3.3481</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5567</v>
+        <v>3.2751</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4678</v>
+        <v>6.3102</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0002</v>
+        <v>3.281</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5567</v>
+        <v>3.2751</v>
       </c>
       <c r="K3" t="n">
         <v>117</v>
@@ -575,7 +575,7 @@
         <v>128</v>
       </c>
       <c r="M3" t="n">
-        <v>6.556900000000001</v>
+        <v>6.556100000000001</v>
       </c>
       <c r="N3" t="n">
         <v>245</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>mouz</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.2804</v>
+        <v>3.7257</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8469</v>
+        <v>0.7372</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2614</v>
+        <v>1.044</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2804</v>
+        <v>3.7257</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1228</v>
+        <v>3.1671</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1576</v>
+        <v>0.5586</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1228</v>
+        <v>5.6726</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3416</v>
+        <v>2.9495</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1576</v>
+        <v>0.5586</v>
       </c>
       <c r="K4" t="n">
         <v>156</v>
@@ -621,7 +621,7 @@
         <v>78</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4992</v>
+        <v>3.5081</v>
       </c>
       <c r="N4" t="n">
         <v>234</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mouz</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9144</v>
+        <v>3.6524</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7745</v>
+        <v>0.7227</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1156</v>
+        <v>1.0109</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9144</v>
+        <v>3.6524</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3666</v>
+        <v>3.4909</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5478</v>
+        <v>0.1615</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3666</v>
+        <v>6.8133</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7287</v>
+        <v>3.5426</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5478</v>
+        <v>0.1615</v>
       </c>
       <c r="K5" t="n">
         <v>156</v>
@@ -667,7 +667,7 @@
         <v>78</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2765</v>
+        <v>3.7041</v>
       </c>
       <c r="N5" t="n">
         <v>234</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6714</v>
+        <v>3.5601</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7264</v>
+        <v>0.7044</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0188</v>
+        <v>0.9692</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6714</v>
+        <v>3.5601</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4496</v>
+        <v>2.6319</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2218</v>
+        <v>0.9282</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4496</v>
+        <v>3.7869</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9855</v>
+        <v>1.969</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2218</v>
+        <v>0.9282</v>
       </c>
       <c r="K6" t="n">
         <v>54</v>
@@ -713,7 +713,7 @@
         <v>132</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2073</v>
+        <v>2.8972</v>
       </c>
       <c r="N6" t="n">
         <v>186</v>
@@ -722,139 +722,139 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8942</v>
+        <v>3.5465</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5726</v>
+        <v>0.7017</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7091</v>
+        <v>0.9631</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8942</v>
+        <v>3.5465</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8851</v>
+        <v>2.3447</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0091</v>
+        <v>1.2018</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8851</v>
+        <v>2.7749</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5279</v>
+        <v>1.4428</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0091</v>
+        <v>1.2018</v>
       </c>
       <c r="K7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L7" t="n">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="M7" t="n">
-        <v>2.537</v>
+        <v>2.6446</v>
       </c>
       <c r="N7" t="n">
-        <v>127</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8783</v>
+        <v>3.2044</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5695</v>
+        <v>0.634</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7028</v>
+        <v>0.8086</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8783</v>
+        <v>3.2044</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7829</v>
+        <v>2.4187</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0954</v>
+        <v>0.7857</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7829</v>
+        <v>3.0357</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4451</v>
+        <v>1.5784</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0954</v>
+        <v>0.7857</v>
       </c>
       <c r="K8" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L8" t="n">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5405</v>
+        <v>2.3641</v>
       </c>
       <c r="N8" t="n">
-        <v>186</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8416</v>
+        <v>3.2035</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5622</v>
+        <v>0.6338</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6882</v>
+        <v>0.8082</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8416</v>
+        <v>3.2035</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8416</v>
+        <v>1.9923</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1.2112</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8416</v>
+        <v>1.9923</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8655</v>
+        <v>1.0359</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.2112</v>
       </c>
       <c r="K9" t="n">
-        <v>200</v>
+        <v>117</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8655</v>
+        <v>2.2471</v>
       </c>
       <c r="N9" t="n">
-        <v>200</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.565</v>
+        <v>2.9618</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5075</v>
+        <v>0.586</v>
       </c>
       <c r="D10" t="n">
-        <v>0.578</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.565</v>
+        <v>2.9618</v>
       </c>
       <c r="F10" t="n">
-        <v>2.565</v>
+        <v>2.9618</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.565</v>
+        <v>3.1439</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5866</v>
+        <v>3.2732</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5866</v>
+        <v>3.2732</v>
       </c>
       <c r="N10" t="n">
         <v>143</v>
@@ -906,492 +906,492 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.7995</v>
+        <v>2.8611</v>
       </c>
       <c r="C11" t="n">
-        <v>0.356</v>
+        <v>0.5661</v>
       </c>
       <c r="D11" t="n">
-        <v>0.273</v>
+        <v>0.6536</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7995</v>
+        <v>2.8611</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7995</v>
+        <v>2.8611</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7995</v>
+        <v>2.9228</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8146</v>
+        <v>3.043</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8146</v>
+        <v>3.043</v>
       </c>
       <c r="N11" t="n">
-        <v>143</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7741</v>
+        <v>2.4024</v>
       </c>
       <c r="C12" t="n">
-        <v>0.351</v>
+        <v>0.4753</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2629</v>
+        <v>0.4465</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7741</v>
+        <v>2.4024</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7741</v>
+        <v>1.4259</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.9765</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7741</v>
+        <v>1.4259</v>
       </c>
       <c r="I12" t="n">
-        <v>1.789</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.9765</v>
       </c>
       <c r="K12" t="n">
-        <v>200</v>
+        <v>117</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M12" t="n">
-        <v>1.789</v>
+        <v>1.7179</v>
       </c>
       <c r="N12" t="n">
-        <v>200</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.6802</v>
+        <v>2.1868</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3324</v>
+        <v>0.4327</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2255</v>
+        <v>0.3492</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6802</v>
+        <v>2.1868</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8332000000000001</v>
+        <v>2.3454</v>
       </c>
       <c r="G13" t="n">
-        <v>0.847</v>
+        <v>-0.1586</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8332000000000001</v>
+        <v>2.7774</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6753</v>
+        <v>1.4441</v>
       </c>
       <c r="J13" t="n">
-        <v>0.847</v>
+        <v>-0.1586</v>
       </c>
       <c r="K13" t="n">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="L13" t="n">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5223</v>
+        <v>1.2855</v>
       </c>
       <c r="N13" t="n">
-        <v>245</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5524</v>
+        <v>2.0761</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3072</v>
+        <v>0.4108</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1746</v>
+        <v>0.2992</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5524</v>
+        <v>2.0761</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8843</v>
+        <v>1.6382</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3319</v>
+        <v>0.4379</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8843</v>
+        <v>1.6382</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5273</v>
+        <v>0.8518</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3319</v>
+        <v>0.4379</v>
       </c>
       <c r="K14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L14" t="n">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1954</v>
+        <v>1.2897</v>
       </c>
       <c r="N14" t="n">
-        <v>127</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>znajder</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5428</v>
+        <v>2.048</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3053</v>
+        <v>0.4052</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1707</v>
+        <v>0.2866</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5428</v>
+        <v>2.048</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5874</v>
+        <v>1.4613</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9554</v>
+        <v>0.5867</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5874</v>
+        <v>1.4613</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4761</v>
+        <v>0.7598</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9554</v>
+        <v>0.5867</v>
       </c>
       <c r="K15" t="n">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="L15" t="n">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4315</v>
+        <v>1.3465</v>
       </c>
       <c r="N15" t="n">
-        <v>245</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>znajder</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.375</v>
+        <v>1.9918</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2721</v>
+        <v>0.3941</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1039</v>
+        <v>0.2612</v>
       </c>
       <c r="E16" t="n">
-        <v>1.375</v>
+        <v>1.9918</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7916</v>
+        <v>1.9918</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5834</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7916</v>
+        <v>1.9918</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6415999999999999</v>
+        <v>2.0737</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5834</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>53</v>
+        <v>200</v>
       </c>
       <c r="L16" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.225</v>
+        <v>2.0737</v>
       </c>
       <c r="N16" t="n">
-        <v>127</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3319</v>
+        <v>1.9663</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2635</v>
+        <v>0.389</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0867</v>
+        <v>0.2497</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3319</v>
+        <v>1.9663</v>
       </c>
       <c r="F17" t="n">
-        <v>0.957</v>
+        <v>0.6647</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3749</v>
+        <v>1.3016</v>
       </c>
       <c r="H17" t="n">
-        <v>0.957</v>
+        <v>0.6647</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.3456</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3749</v>
+        <v>1.3016</v>
       </c>
       <c r="K17" t="n">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="L17" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1506</v>
+        <v>1.6472</v>
       </c>
       <c r="N17" t="n">
-        <v>186</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2705</v>
+        <v>1.8154</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2514</v>
+        <v>0.3592</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0623</v>
+        <v>0.1815</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2705</v>
+        <v>1.8154</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2705</v>
+        <v>1.8154</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2705</v>
+        <v>1.8154</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2705</v>
+        <v>1.8901</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2705</v>
+        <v>1.8901</v>
       </c>
       <c r="N18" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1707</v>
+        <v>1.5524</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2316</v>
+        <v>0.3072</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0225</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1707</v>
+        <v>1.5524</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1707</v>
+        <v>2.2815</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.7291</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1707</v>
+        <v>2.5521</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1707</v>
+        <v>1.327</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.7291</v>
       </c>
       <c r="K19" t="n">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1707</v>
+        <v>0.5979</v>
       </c>
       <c r="N19" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.106</v>
+        <v>1.4085</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2188</v>
+        <v>0.2787</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0033</v>
+        <v>-0.0021</v>
       </c>
       <c r="E20" t="n">
-        <v>1.106</v>
+        <v>1.4085</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0866</v>
+        <v>1.4085</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1926</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0866</v>
+        <v>1.4085</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0702</v>
+        <v>1.4664</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1926</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="L20" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1224</v>
+        <v>1.4664</v>
       </c>
       <c r="N20" t="n">
-        <v>245</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.2687</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1351</v>
+        <v>0.251</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1718</v>
+        <v>-0.0653</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.2687</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.2687</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.2687</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.2687</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.2687</v>
       </c>
       <c r="N21" t="n">
         <v>131</v>
@@ -1412,308 +1412,308 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6389</v>
+        <v>1.2443</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1264</v>
+        <v>0.2462</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1894</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6389</v>
+        <v>1.2443</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6389</v>
+        <v>1.2443</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6389</v>
+        <v>1.2443</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6443</v>
+        <v>1.2443</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6443</v>
+        <v>1.2443</v>
       </c>
       <c r="N22" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6072</v>
+        <v>1.0924</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1201</v>
+        <v>0.2161</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.202</v>
+        <v>-0.1449</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6072</v>
+        <v>1.0924</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6072</v>
+        <v>1.0924</v>
       </c>
       <c r="G23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.6072</v>
+        <v>1.0924</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3027</v>
+        <v>1.0924</v>
       </c>
       <c r="J23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="L23" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3027</v>
+        <v>1.0924</v>
       </c>
       <c r="N23" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5433</v>
+        <v>1.0485</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1075</v>
+        <v>0.2075</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2275</v>
+        <v>-0.1647</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5433</v>
+        <v>1.0485</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5433</v>
+        <v>1.0485</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5433</v>
+        <v>1.0485</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5433</v>
+        <v>1.0916</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5433</v>
+        <v>1.0916</v>
       </c>
       <c r="N24" t="n">
-        <v>72</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>Furlan</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2986</v>
+        <v>1.0154</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0591</v>
+        <v>0.2009</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3249</v>
+        <v>-0.1796</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2986</v>
+        <v>1.0154</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2986</v>
+        <v>0.881</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.1344</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2986</v>
+        <v>0.881</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3012</v>
+        <v>0.4581</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.1344</v>
       </c>
       <c r="K25" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3012</v>
+        <v>0.5925</v>
       </c>
       <c r="N25" t="n">
-        <v>143</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>SZPERO</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2194</v>
+        <v>0.8928</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0434</v>
+        <v>0.1766</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3565</v>
+        <v>-0.235</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2194</v>
+        <v>0.8928</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2194</v>
+        <v>0.507</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.3858</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2194</v>
+        <v>0.507</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2212</v>
+        <v>0.2636</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.3858</v>
       </c>
       <c r="K26" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2212</v>
+        <v>0.6494</v>
       </c>
       <c r="N26" t="n">
-        <v>143</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SZPERO</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1944</v>
+        <v>0.6704</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0385</v>
+        <v>0.1326</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3665</v>
+        <v>-0.3354</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1944</v>
+        <v>0.6704</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1129</v>
+        <v>0.6704</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3073</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1129</v>
+        <v>0.6704</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0915</v>
+        <v>0.698</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3073</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="L27" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2158</v>
+        <v>0.698</v>
       </c>
       <c r="N27" t="n">
-        <v>234</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1432</v>
+        <v>0.5746</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0283</v>
+        <v>0.1137</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3869</v>
+        <v>-0.3786</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1432</v>
+        <v>0.5746</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1432</v>
+        <v>0.5746</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1432</v>
+        <v>0.5746</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1432</v>
+        <v>0.5746</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1432</v>
+        <v>0.5746</v>
       </c>
       <c r="N28" t="n">
         <v>72</v>
@@ -1734,47 +1734,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Furlan</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1286</v>
+        <v>0.4399</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0254</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3927</v>
+        <v>-0.4394</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1286</v>
+        <v>0.4399</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1323</v>
+        <v>0.4399</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0037</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1323</v>
+        <v>0.4399</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1072</v>
+        <v>0.458</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0037</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="L29" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1035</v>
+        <v>0.458</v>
       </c>
       <c r="N29" t="n">
-        <v>234</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0504</v>
+        <v>0.3744</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01</v>
+        <v>0.0741</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4238</v>
+        <v>-0.469</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0504</v>
+        <v>0.3744</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0504</v>
+        <v>0.3744</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0504</v>
+        <v>0.3744</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0508</v>
+        <v>0.3898</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0508</v>
+        <v>0.3898</v>
       </c>
       <c r="N30" t="n">
         <v>200</v>
@@ -1826,78 +1826,78 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.3051</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0153</v>
+        <v>0.0604</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4747</v>
+        <v>-0.5003</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.3051</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.3051</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.3051</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.078</v>
+        <v>0.3051</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>200</v>
+        <v>72</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.078</v>
+        <v>0.3051</v>
       </c>
       <c r="N31" t="n">
-        <v>200</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1093</v>
+        <v>0.2112</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0216</v>
+        <v>0.0418</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4875</v>
+        <v>-0.5427</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1093</v>
+        <v>0.2112</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1093</v>
+        <v>0.2112</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1093</v>
+        <v>0.2112</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1093</v>
+        <v>0.2112</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1093</v>
+        <v>0.2112</v>
       </c>
       <c r="N32" t="n">
         <v>72</v>
@@ -1918,32 +1918,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.1682</v>
+        <v>0.1479</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0333</v>
+        <v>0.0293</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5109</v>
+        <v>-0.5712</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1682</v>
+        <v>0.1479</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1682</v>
+        <v>0.1479</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1682</v>
+        <v>0.1479</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1682</v>
+        <v>0.1479</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1682</v>
+        <v>0.1479</v>
       </c>
       <c r="N33" t="n">
         <v>72</v>
@@ -1964,35 +1964,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yam</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.2149</v>
+        <v>0.1085</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0425</v>
+        <v>0.0215</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5295</v>
+        <v>-0.589</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2149</v>
+        <v>0.1085</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.386</v>
+        <v>0.758</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1711</v>
+        <v>-0.6495</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.386</v>
+        <v>0.758</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3129</v>
+        <v>0.3941</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1711</v>
+        <v>-0.6495</v>
       </c>
       <c r="K34" t="n">
         <v>54</v>
@@ -2001,7 +2001,7 @@
         <v>132</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1418</v>
+        <v>-0.2554</v>
       </c>
       <c r="N34" t="n">
         <v>186</v>
@@ -2010,35 +2010,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>yam</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6723</v>
+        <v>-0.2922</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.133</v>
+        <v>-0.0578</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7118</v>
+        <v>-0.7699</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6723</v>
+        <v>-0.2922</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4028</v>
+        <v>-0.3393</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.0751</v>
+        <v>0.0471</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4028</v>
+        <v>-0.3393</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3265</v>
+        <v>-0.1764</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.0751</v>
+        <v>0.0471</v>
       </c>
       <c r="K35" t="n">
         <v>54</v>
@@ -2047,7 +2047,7 @@
         <v>132</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7485999999999999</v>
+        <v>-0.1293</v>
       </c>
       <c r="N35" t="n">
         <v>186</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9058</v>
+        <v>-0.5502</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1792</v>
+        <v>-0.1089</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8048</v>
+        <v>-0.8864</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9058</v>
+        <v>-0.5502</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9058</v>
+        <v>-0.5502</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9058</v>
+        <v>-0.5502</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9058</v>
+        <v>-0.5502</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9058</v>
+        <v>-0.5502</v>
       </c>
       <c r="N36" t="n">
         <v>131</v>
@@ -2102,32 +2102,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9421</v>
+        <v>-0.5664</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1864</v>
+        <v>-0.1121</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8192</v>
+        <v>-0.8937</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9421</v>
+        <v>-0.5664</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9421</v>
+        <v>-0.5664</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9421</v>
+        <v>-0.5664</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9421</v>
+        <v>-0.5664</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9421</v>
+        <v>-0.5664</v>
       </c>
       <c r="N37" t="n">
         <v>131</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.5393</v>
+        <v>-1.4308</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3046</v>
+        <v>-0.2831</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0572</v>
+        <v>-1.2839</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.5393</v>
+        <v>-1.4308</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8096</v>
+        <v>-0.9853</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.7297</v>
+        <v>-0.4455</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8096</v>
+        <v>-0.9853</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6562</v>
+        <v>-0.5123</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7297</v>
+        <v>-0.4455</v>
       </c>
       <c r="K38" t="n">
         <v>53</v>
@@ -2185,7 +2185,7 @@
         <v>74</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3859</v>
+        <v>-0.9578</v>
       </c>
       <c r="N38" t="n">
         <v>127</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7009</v>
+        <v>-1.471</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3365</v>
+        <v>-0.291</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1215</v>
+        <v>-1.3021</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7009</v>
+        <v>-1.471</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.7009</v>
+        <v>-1.471</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.7009</v>
+        <v>-1.471</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.7009</v>
+        <v>-1.471</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.7009</v>
+        <v>-1.471</v>
       </c>
       <c r="N39" t="n">
         <v>72</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rallen</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.4369</v>
+        <v>-1.9075</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4822</v>
+        <v>-0.3774</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4148</v>
+        <v>-1.4992</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.4369</v>
+        <v>-1.9075</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0415</v>
+        <v>-1.9075</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.3954</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0415</v>
+        <v>-1.9075</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.6547</v>
+        <v>-1.986</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.3954</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>156</v>
+        <v>200</v>
       </c>
       <c r="L40" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.0501</v>
+        <v>-1.986</v>
       </c>
       <c r="N40" t="n">
-        <v>234</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>rallen</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.6575</v>
+        <v>-2.4976</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5258</v>
+        <v>-0.4942</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5027</v>
+        <v>-1.7656</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.6575</v>
+        <v>-2.4976</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.6575</v>
+        <v>-2.3993</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.0983</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.6575</v>
+        <v>-2.3993</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.6799</v>
+        <v>-1.2475</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.0983</v>
       </c>
       <c r="K41" t="n">
-        <v>200</v>
+        <v>156</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.6799</v>
+        <v>-1.3458</v>
       </c>
       <c r="N41" t="n">
-        <v>200</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.57</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8589</v>
+        <v>1.0546</v>
       </c>
       <c r="J2" t="n">
-        <v>24.0492</v>
+        <v>29.5288</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.92</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1743</v>
+        <v>-0.1069</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.8804</v>
+        <v>-2.9932</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.86</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2795</v>
+        <v>-0.1721</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.826</v>
+        <v>-4.8188</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.85</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2956</v>
+        <v>-0.1826</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.2768</v>
+        <v>-5.1128</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.57</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6754</v>
+        <v>-0.4518</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.9112</v>
+        <v>-12.6504</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.45</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1105</v>
+        <v>1.0725</v>
       </c>
       <c r="J7" t="n">
-        <v>31.094</v>
+        <v>30.03</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0052</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>28.1456</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.31</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8037</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>22.5036</v>
+        <v>22.708</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.98</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2305</v>
+        <v>-0.1497</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.454</v>
+        <v>-4.1916</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.96</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3022</v>
+        <v>-0.222</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.461600000000001</v>
+        <v>-6.216</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.08</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2676</v>
+        <v>0.2723</v>
       </c>
       <c r="J12" t="n">
-        <v>6.9576</v>
+        <v>7.0798</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.88</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1612</v>
+        <v>-0.1354</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.1912</v>
+        <v>-3.5204</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.83</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2497</v>
+        <v>-0.1877</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.4922</v>
+        <v>-4.8802</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.66</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.3498</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.7722</v>
+        <v>-9.094799999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.6</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6102</v>
+        <v>-0.4061</v>
       </c>
       <c r="J16" t="n">
-        <v>-15.8652</v>
+        <v>-10.5586</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.49</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1444</v>
+        <v>1.1042</v>
       </c>
       <c r="J17" t="n">
-        <v>29.7544</v>
+        <v>28.7092</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.44</v>
       </c>
       <c r="I18" t="n">
-        <v>1.04</v>
+        <v>1.0407</v>
       </c>
       <c r="J18" t="n">
-        <v>27.04</v>
+        <v>27.0582</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.29</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6708</v>
+        <v>0.7487</v>
       </c>
       <c r="J19" t="n">
-        <v>17.4408</v>
+        <v>19.4662</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.24</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5466</v>
+        <v>0.634</v>
       </c>
       <c r="J20" t="n">
-        <v>14.2116</v>
+        <v>16.484</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.13</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2695</v>
+        <v>0.3578</v>
       </c>
       <c r="J21" t="n">
-        <v>7.007</v>
+        <v>9.3028</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.95</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0287</v>
+        <v>-0.0153</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6027</v>
+        <v>-0.3213</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.71</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3717</v>
+        <v>-0.2853</v>
       </c>
       <c r="J23" t="n">
-        <v>-7.8057</v>
+        <v>-5.9913</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.67</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4516</v>
+        <v>-0.3213</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.483599999999999</v>
+        <v>-6.7473</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.54</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6514</v>
+        <v>-0.4413</v>
       </c>
       <c r="J25" t="n">
-        <v>-13.6794</v>
+        <v>-9.267300000000001</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.51</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-0.4694</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.532</v>
+        <v>-9.8574</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.86</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7304</v>
+        <v>1.2288</v>
       </c>
       <c r="J27" t="n">
-        <v>36.3384</v>
+        <v>25.8048</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.8</v>
       </c>
       <c r="I28" t="n">
-        <v>1.642</v>
+        <v>1.1614</v>
       </c>
       <c r="J28" t="n">
-        <v>34.482</v>
+        <v>24.3894</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.46</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9475</v>
+        <v>0.7716</v>
       </c>
       <c r="J29" t="n">
-        <v>19.8975</v>
+        <v>16.2036</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.26</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5169</v>
+        <v>0.5139</v>
       </c>
       <c r="J30" t="n">
-        <v>10.8549</v>
+        <v>10.7919</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.23</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4495</v>
+        <v>0.4719</v>
       </c>
       <c r="J31" t="n">
-        <v>9.439500000000001</v>
+        <v>9.9099</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.53</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7266</v>
+        <v>0.5195</v>
       </c>
       <c r="J32" t="n">
-        <v>17.4384</v>
+        <v>12.468</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.47</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6573</v>
+        <v>0.4812</v>
       </c>
       <c r="J33" t="n">
-        <v>15.7752</v>
+        <v>11.5488</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.221</v>
+        <v>0.2289</v>
       </c>
       <c r="J34" t="n">
-        <v>5.304</v>
+        <v>5.4936</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0207</v>
+        <v>0.0555</v>
       </c>
       <c r="J35" t="n">
-        <v>0.4968</v>
+        <v>1.332</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.98</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1355</v>
+        <v>-0.0591</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.252</v>
+        <v>-1.4184</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.19</v>
       </c>
       <c r="I37" t="n">
-        <v>0.418</v>
+        <v>0.3506</v>
       </c>
       <c r="J37" t="n">
-        <v>10.032</v>
+        <v>8.414400000000001</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.89</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1727</v>
+        <v>-0.1321</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.1448</v>
+        <v>-3.1704</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.86</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2381</v>
+        <v>-0.1628</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.7144</v>
+        <v>-3.9072</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.78</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3744</v>
+        <v>-0.2423</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.9856</v>
+        <v>-5.8152</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.61</v>
+        <v>-0.4044</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.64</v>
+        <v>-9.7056</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.35</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5775</v>
+        <v>0.5468</v>
       </c>
       <c r="J42" t="n">
-        <v>16.7475</v>
+        <v>15.8572</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.12</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2538</v>
+        <v>0.2815</v>
       </c>
       <c r="J43" t="n">
-        <v>7.3602</v>
+        <v>8.163500000000001</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.93</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1812</v>
+        <v>-0.1022</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.2548</v>
+        <v>-2.9638</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.86</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2988</v>
+        <v>-0.1797</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.6652</v>
+        <v>-5.2113</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.84</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3294</v>
+        <v>-0.2006</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.5526</v>
+        <v>-5.8174</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.42</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1143</v>
+        <v>0.7915</v>
       </c>
       <c r="J47" t="n">
-        <v>32.3147</v>
+        <v>22.9535</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.19</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5857</v>
+        <v>0.4674</v>
       </c>
       <c r="J48" t="n">
-        <v>16.9853</v>
+        <v>13.5546</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.11</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3578</v>
+        <v>0.3433</v>
       </c>
       <c r="J49" t="n">
-        <v>10.3762</v>
+        <v>9.9557</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.98</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1785</v>
+        <v>-0.1166</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.1765</v>
+        <v>-3.3814</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.76</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7952</v>
+        <v>-0.75</v>
       </c>
       <c r="J51" t="n">
-        <v>-23.0608</v>
+        <v>-21.75</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.04</v>
       </c>
       <c r="I52" t="n">
-        <v>0.167</v>
+        <v>0.1152</v>
       </c>
       <c r="J52" t="n">
-        <v>4.175</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.95</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0612</v>
+        <v>-0.0634</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.53</v>
+        <v>-1.585</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.91</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1391</v>
+        <v>-0.111</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.4775</v>
+        <v>-2.775</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.89</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1778</v>
+        <v>-0.1329</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.445</v>
+        <v>-3.3225</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.58</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6496</v>
+        <v>-0.4333</v>
       </c>
       <c r="J56" t="n">
-        <v>-16.24</v>
+        <v>-10.8325</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.51</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6921</v>
+        <v>0.5023</v>
       </c>
       <c r="J57" t="n">
-        <v>17.3025</v>
+        <v>12.5575</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.48</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6572</v>
+        <v>0.4833</v>
       </c>
       <c r="J58" t="n">
-        <v>16.43</v>
+        <v>12.0825</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.4</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5603</v>
+        <v>0.4323</v>
       </c>
       <c r="J59" t="n">
-        <v>14.0075</v>
+        <v>10.8075</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.12</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1482</v>
+        <v>0.1709</v>
       </c>
       <c r="J60" t="n">
-        <v>3.705</v>
+        <v>4.2725</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.88</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3165</v>
+        <v>-0.1843</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.9125</v>
+        <v>-4.6075</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.62</v>
       </c>
       <c r="I62" t="n">
-        <v>1.3711</v>
+        <v>0.9774</v>
       </c>
       <c r="J62" t="n">
-        <v>31.5353</v>
+        <v>22.4802</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.47</v>
       </c>
       <c r="I63" t="n">
-        <v>1.0703</v>
+        <v>0.7963</v>
       </c>
       <c r="J63" t="n">
-        <v>24.6169</v>
+        <v>18.3149</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.43</v>
       </c>
       <c r="I64" t="n">
-        <v>0.9825</v>
+        <v>0.7473</v>
       </c>
       <c r="J64" t="n">
-        <v>22.5975</v>
+        <v>17.1879</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.32</v>
       </c>
       <c r="I65" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.6109</v>
       </c>
       <c r="J65" t="n">
-        <v>16.2173</v>
+        <v>14.0507</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.07</v>
       </c>
       <c r="I66" t="n">
-        <v>0.0838</v>
+        <v>0.1725</v>
       </c>
       <c r="J66" t="n">
-        <v>1.9274</v>
+        <v>3.9675</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3143</v>
+        <v>0.33</v>
       </c>
       <c r="J67" t="n">
-        <v>7.2289</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.78</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3256</v>
+        <v>-0.2325</v>
       </c>
       <c r="J68" t="n">
-        <v>-7.4888</v>
+        <v>-5.3475</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.76</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3662</v>
+        <v>-0.251</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.422599999999999</v>
+        <v>-5.773</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.75</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3834</v>
+        <v>-0.2604</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.818199999999999</v>
+        <v>-5.9892</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.51</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7181999999999999</v>
+        <v>-0.4855</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.5186</v>
+        <v>-11.1665</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.33</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9494</v>
+        <v>0.6826</v>
       </c>
       <c r="J72" t="n">
-        <v>28.482</v>
+        <v>20.478</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.27</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.5967</v>
       </c>
       <c r="J73" t="n">
-        <v>24.39</v>
+        <v>17.901</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.294</v>
+        <v>-0.2399</v>
       </c>
       <c r="J74" t="n">
-        <v>-8.82</v>
+        <v>-7.197</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.92</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3572</v>
+        <v>-0.3014</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.716</v>
+        <v>-9.042</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.74</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.786</v>
       </c>
       <c r="J76" t="n">
-        <v>-24.783</v>
+        <v>-23.58</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.2</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3683</v>
+        <v>0.388</v>
       </c>
       <c r="J77" t="n">
-        <v>11.049</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.19</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3537</v>
+        <v>0.3773</v>
       </c>
       <c r="J78" t="n">
-        <v>10.611</v>
+        <v>11.319</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.08</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1737</v>
+        <v>0.196</v>
       </c>
       <c r="J79" t="n">
-        <v>5.211</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.95</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1511</v>
+        <v>-0.0804</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.533</v>
+        <v>-2.412</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3932</v>
+        <v>-0.244</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.796</v>
+        <v>-7.32</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.01</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1752</v>
+        <v>0.1175</v>
       </c>
       <c r="J82" t="n">
-        <v>3.8544</v>
+        <v>2.585</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.78</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2704</v>
+        <v>-0.2204</v>
       </c>
       <c r="J83" t="n">
-        <v>-5.9488</v>
+        <v>-4.8488</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.61</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.3796</v>
       </c>
       <c r="J84" t="n">
-        <v>-12.342</v>
+        <v>-8.3512</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.61</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.3796</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.342</v>
+        <v>-8.3512</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.48</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7373</v>
+        <v>-0.5011</v>
       </c>
       <c r="J86" t="n">
-        <v>-16.2206</v>
+        <v>-11.0242</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.94</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1122</v>
+        <v>1.0147</v>
       </c>
       <c r="J87" t="n">
-        <v>24.4684</v>
+        <v>22.3234</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.61</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7734</v>
+        <v>0.705</v>
       </c>
       <c r="J88" t="n">
-        <v>17.0148</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.3</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3746</v>
+        <v>0.3806</v>
       </c>
       <c r="J89" t="n">
-        <v>8.241199999999999</v>
+        <v>8.373200000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.15</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1696</v>
+        <v>0.198</v>
       </c>
       <c r="J90" t="n">
-        <v>3.7312</v>
+        <v>4.356</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.98</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1603</v>
+        <v>-0.0731</v>
       </c>
       <c r="J91" t="n">
-        <v>-3.5266</v>
+        <v>-1.6082</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>1.9362</v>
+        <v>1.6427</v>
       </c>
       <c r="J92" t="n">
-        <v>34.8516</v>
+        <v>29.5686</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.83</v>
       </c>
       <c r="I93" t="n">
-        <v>1.6647</v>
+        <v>1.4563</v>
       </c>
       <c r="J93" t="n">
-        <v>29.9646</v>
+        <v>26.2134</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.58</v>
       </c>
       <c r="I94" t="n">
-        <v>1.1642</v>
+        <v>1.1784</v>
       </c>
       <c r="J94" t="n">
-        <v>20.9556</v>
+        <v>21.2112</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.44</v>
       </c>
       <c r="I95" t="n">
-        <v>0.8739</v>
+        <v>1.0067</v>
       </c>
       <c r="J95" t="n">
-        <v>15.7302</v>
+        <v>18.1206</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.15</v>
       </c>
       <c r="I96" t="n">
-        <v>0.2437</v>
+        <v>0.3527</v>
       </c>
       <c r="J96" t="n">
-        <v>4.3866</v>
+        <v>6.3486</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3961</v>
+        <v>0.4833</v>
       </c>
       <c r="J97" t="n">
-        <v>7.1298</v>
+        <v>8.699400000000001</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.59</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.4896</v>
+        <v>-0.3762</v>
       </c>
       <c r="J98" t="n">
-        <v>-8.812799999999999</v>
+        <v>-6.7716</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.47</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.7032</v>
+        <v>-0.4848</v>
       </c>
       <c r="J99" t="n">
-        <v>-12.6576</v>
+        <v>-8.7264</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.38</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.8285</v>
+        <v>-0.5712</v>
       </c>
       <c r="J100" t="n">
-        <v>-14.913</v>
+        <v>-10.2816</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.27</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.9698</v>
+        <v>-0.6787</v>
       </c>
       <c r="J101" t="n">
-        <v>-17.4564</v>
+        <v>-12.2166</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.36</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9393</v>
+        <v>0.9352</v>
       </c>
       <c r="J102" t="n">
-        <v>25.3611</v>
+        <v>25.2504</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.33</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8724</v>
+        <v>0.8685</v>
       </c>
       <c r="J103" t="n">
-        <v>23.5548</v>
+        <v>23.4495</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.26</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7077</v>
+        <v>0.7058</v>
       </c>
       <c r="J104" t="n">
-        <v>19.1079</v>
+        <v>19.0566</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.01</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.057</v>
+        <v>0.0113</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.539</v>
+        <v>0.3051</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3533</v>
+        <v>-0.2776</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.539099999999999</v>
+        <v>-7.4952</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.11</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2871</v>
+        <v>0.3029</v>
       </c>
       <c r="J107" t="n">
-        <v>7.7517</v>
+        <v>8.1783</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.09</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2537</v>
+        <v>0.2604</v>
       </c>
       <c r="J108" t="n">
-        <v>6.8499</v>
+        <v>7.0308</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.89</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.189</v>
+        <v>-0.134</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.103</v>
+        <v>-3.618</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.7</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4963</v>
+        <v>-0.3226</v>
       </c>
       <c r="J110" t="n">
-        <v>-13.4001</v>
+        <v>-8.7102</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.65</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.3699</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.201</v>
+        <v>-9.987299999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.08</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2186</v>
+        <v>0.1705</v>
       </c>
       <c r="J112" t="n">
-        <v>7.651</v>
+        <v>5.9675</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.05</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1629</v>
+        <v>0.1189</v>
       </c>
       <c r="J113" t="n">
-        <v>5.7015</v>
+        <v>4.1615</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1217</v>
+        <v>0.0815</v>
       </c>
       <c r="J114" t="n">
-        <v>4.2595</v>
+        <v>2.8525</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.91</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1835</v>
+        <v>-0.1162</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.4225</v>
+        <v>-4.067</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.6</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6355</v>
+        <v>-0.422</v>
       </c>
       <c r="J116" t="n">
-        <v>-22.2425</v>
+        <v>-14.77</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.33</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.4384</v>
       </c>
       <c r="J117" t="n">
-        <v>17.6575</v>
+        <v>15.344</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.21</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3369</v>
+        <v>0.2963</v>
       </c>
       <c r="J118" t="n">
-        <v>11.7915</v>
+        <v>10.3705</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.17</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2676</v>
+        <v>0.2476</v>
       </c>
       <c r="J119" t="n">
-        <v>9.366</v>
+        <v>8.666</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.11</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1619</v>
+        <v>0.1696</v>
       </c>
       <c r="J120" t="n">
-        <v>5.6665</v>
+        <v>5.936</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.03</v>
       </c>
       <c r="I121" t="n">
-        <v>0.0158</v>
+        <v>0.0463</v>
       </c>
       <c r="J121" t="n">
-        <v>0.553</v>
+        <v>1.6205</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.36</v>
       </c>
       <c r="I122" t="n">
-        <v>0.967</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="J122" t="n">
-        <v>28.043</v>
+        <v>27.6399</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.23</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6653</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="J123" t="n">
-        <v>19.2937</v>
+        <v>18.8123</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.2</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5887</v>
+        <v>0.575</v>
       </c>
       <c r="J124" t="n">
-        <v>17.0723</v>
+        <v>16.675</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.02</v>
       </c>
       <c r="I125" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="J125" t="n">
-        <v>0.2552</v>
+        <v>1.9024</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6374</v>
+        <v>-0.5785</v>
       </c>
       <c r="J126" t="n">
-        <v>-18.4846</v>
+        <v>-16.7765</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.45</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6938</v>
+        <v>0.8549</v>
       </c>
       <c r="J127" t="n">
-        <v>20.1202</v>
+        <v>24.7921</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1958</v>
+        <v>0.218</v>
       </c>
       <c r="J128" t="n">
-        <v>5.6782</v>
+        <v>6.322</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.06</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1384</v>
+        <v>0.1551</v>
       </c>
       <c r="J129" t="n">
-        <v>4.0136</v>
+        <v>4.4979</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1677</v>
+        <v>-0.0919</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.8633</v>
+        <v>-2.6651</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.64</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6021</v>
+        <v>-0.3962</v>
       </c>
       <c r="J131" t="n">
-        <v>-17.4609</v>
+        <v>-11.4898</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.69</v>
       </c>
       <c r="I132" t="n">
-        <v>1.5269</v>
+        <v>1.3463</v>
       </c>
       <c r="J132" t="n">
-        <v>33.5918</v>
+        <v>29.6186</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.42</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9926</v>
+        <v>1.0101</v>
       </c>
       <c r="J133" t="n">
-        <v>21.8372</v>
+        <v>22.2222</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.27</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6159</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="J134" t="n">
-        <v>13.5498</v>
+        <v>15.4462</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.23</v>
       </c>
       <c r="I135" t="n">
-        <v>0.5182</v>
+        <v>0.6087</v>
       </c>
       <c r="J135" t="n">
-        <v>11.4004</v>
+        <v>13.3914</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.02</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0643</v>
+        <v>0.0172</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.4146</v>
+        <v>0.3784</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.2</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4483</v>
+        <v>0.5144</v>
       </c>
       <c r="J137" t="n">
-        <v>9.8626</v>
+        <v>11.3168</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2951</v>
+        <v>0.3089</v>
       </c>
       <c r="J138" t="n">
-        <v>6.4922</v>
+        <v>6.7958</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0925</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.1362</v>
+        <v>-2.035</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.47</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.7754</v>
+        <v>-0.5282</v>
       </c>
       <c r="J140" t="n">
-        <v>-17.0588</v>
+        <v>-11.6204</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.44</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.5555</v>
       </c>
       <c r="J141" t="n">
-        <v>-17.842</v>
+        <v>-12.221</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.59</v>
       </c>
       <c r="I142" t="n">
-        <v>1.3326</v>
+        <v>1.223</v>
       </c>
       <c r="J142" t="n">
-        <v>31.9824</v>
+        <v>29.352</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.54</v>
       </c>
       <c r="I143" t="n">
-        <v>1.2347</v>
+        <v>1.1621</v>
       </c>
       <c r="J143" t="n">
-        <v>29.6328</v>
+        <v>27.8904</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.5</v>
       </c>
       <c r="I144" t="n">
-        <v>1.1541</v>
+        <v>1.113</v>
       </c>
       <c r="J144" t="n">
-        <v>27.6984</v>
+        <v>26.712</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.08</v>
       </c>
       <c r="I145" t="n">
-        <v>0.125</v>
+        <v>0.2119</v>
       </c>
       <c r="J145" t="n">
-        <v>3</v>
+        <v>5.0856</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.99</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2244</v>
+        <v>-0.1368</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.3856</v>
+        <v>-3.2832</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.12</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3189</v>
+        <v>0.3411</v>
       </c>
       <c r="J147" t="n">
-        <v>7.6536</v>
+        <v>8.186400000000001</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.88</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.181</v>
+        <v>-0.1407</v>
       </c>
       <c r="J148" t="n">
-        <v>-4.344</v>
+        <v>-3.3768</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.86</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2189</v>
+        <v>-0.1615</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.2536</v>
+        <v>-3.876</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.83</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2837</v>
+        <v>-0.1909</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.8088</v>
+        <v>-4.5816</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.55</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.4576</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.368</v>
+        <v>-10.9824</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.61</v>
       </c>
       <c r="I152" t="n">
-        <v>1.3448</v>
+        <v>1.2364</v>
       </c>
       <c r="J152" t="n">
-        <v>29.5856</v>
+        <v>27.2008</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.54</v>
       </c>
       <c r="I153" t="n">
-        <v>1.2072</v>
+        <v>1.1526</v>
       </c>
       <c r="J153" t="n">
-        <v>26.5584</v>
+        <v>25.3572</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.46</v>
       </c>
       <c r="I154" t="n">
-        <v>1.0398</v>
+        <v>1.0556</v>
       </c>
       <c r="J154" t="n">
-        <v>22.8756</v>
+        <v>23.2232</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.45</v>
       </c>
       <c r="I155" t="n">
-        <v>1.0177</v>
+        <v>1.0427</v>
       </c>
       <c r="J155" t="n">
-        <v>22.3894</v>
+        <v>22.9394</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.93</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4409</v>
+        <v>-0.3589</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.6998</v>
+        <v>-7.8958</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.19</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4388</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>9.653600000000001</v>
+        <v>11.033</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.96</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0144</v>
+        <v>-0.0396</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.3168</v>
+        <v>-0.8712</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.78</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3517</v>
+        <v>-0.2359</v>
       </c>
       <c r="J159" t="n">
-        <v>-7.7374</v>
+        <v>-5.1898</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.7</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4746</v>
+        <v>-0.3125</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.4412</v>
+        <v>-6.875</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.44</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.8092</v>
+        <v>-0.5541</v>
       </c>
       <c r="J161" t="n">
-        <v>-17.8024</v>
+        <v>-12.1902</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.29</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5265</v>
+        <v>0.6227</v>
       </c>
       <c r="J162" t="n">
-        <v>15.795</v>
+        <v>18.681</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.17</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3596</v>
+        <v>0.4016</v>
       </c>
       <c r="J163" t="n">
-        <v>10.788</v>
+        <v>12.048</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.96</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.059</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.262</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.95</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0988</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J165" t="n">
-        <v>-2.964</v>
+        <v>-2.142</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.35</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.9258999999999999</v>
+        <v>-0.6469</v>
       </c>
       <c r="J166" t="n">
-        <v>-27.777</v>
+        <v>-19.407</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.4</v>
       </c>
       <c r="I167" t="n">
-        <v>1.028</v>
+        <v>1.0117</v>
       </c>
       <c r="J167" t="n">
-        <v>30.84</v>
+        <v>30.351</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.39</v>
       </c>
       <c r="I168" t="n">
-        <v>1.0066</v>
+        <v>0.9947</v>
       </c>
       <c r="J168" t="n">
-        <v>30.198</v>
+        <v>29.841</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.34</v>
       </c>
       <c r="I169" t="n">
-        <v>0.897</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="J169" t="n">
-        <v>26.91</v>
+        <v>26.778</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.95</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3203</v>
+        <v>-0.2443</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.609</v>
+        <v>-7.329</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7239</v>
+        <v>-0.6693</v>
       </c>
       <c r="J171" t="n">
-        <v>-21.717</v>
+        <v>-20.079</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.4</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6089</v>
+        <v>0.5298</v>
       </c>
       <c r="J172" t="n">
-        <v>17.6581</v>
+        <v>15.3642</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.34</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5342</v>
+        <v>0.4601</v>
       </c>
       <c r="J173" t="n">
-        <v>15.4918</v>
+        <v>13.3429</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3722</v>
+        <v>0.3157</v>
       </c>
       <c r="J174" t="n">
-        <v>10.7938</v>
+        <v>9.1553</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.91</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2413</v>
+        <v>-0.1356</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.9977</v>
+        <v>-3.9324</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.71</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5259</v>
+        <v>-0.3388</v>
       </c>
       <c r="J176" t="n">
-        <v>-15.2511</v>
+        <v>-9.825200000000001</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.17</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3531</v>
+        <v>0.3024</v>
       </c>
       <c r="J177" t="n">
-        <v>10.2399</v>
+        <v>8.769600000000001</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.11</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2591</v>
+        <v>0.2121</v>
       </c>
       <c r="J178" t="n">
-        <v>7.5139</v>
+        <v>6.1509</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.01</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0608</v>
+        <v>0.0339</v>
       </c>
       <c r="J179" t="n">
-        <v>1.7632</v>
+        <v>0.9831</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.76</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4315</v>
+        <v>-0.2741</v>
       </c>
       <c r="J180" t="n">
-        <v>-12.5135</v>
+        <v>-7.9489</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.76</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4315</v>
+        <v>-0.2741</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.5135</v>
+        <v>-7.9489</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.3</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5189</v>
+        <v>0.6156</v>
       </c>
       <c r="J182" t="n">
-        <v>15.567</v>
+        <v>18.468</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.26</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4659</v>
+        <v>0.5455</v>
       </c>
       <c r="J183" t="n">
-        <v>13.977</v>
+        <v>16.365</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.02</v>
       </c>
       <c r="I184" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.0654</v>
       </c>
       <c r="J184" t="n">
-        <v>1.971</v>
+        <v>1.962</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1941</v>
+        <v>-0.1121</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.823</v>
+        <v>-3.363</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.52</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7412</v>
+        <v>-0.5019</v>
       </c>
       <c r="J186" t="n">
-        <v>-22.236</v>
+        <v>-15.057</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.27</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.7678</v>
       </c>
       <c r="J187" t="n">
-        <v>23.907</v>
+        <v>23.034</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.27</v>
       </c>
       <c r="I188" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.7678</v>
       </c>
       <c r="J188" t="n">
-        <v>23.907</v>
+        <v>23.034</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.16</v>
       </c>
       <c r="I189" t="n">
-        <v>0.5214</v>
+        <v>0.4906</v>
       </c>
       <c r="J189" t="n">
-        <v>15.642</v>
+        <v>14.718</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.83</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.6176</v>
+        <v>-0.5621</v>
       </c>
       <c r="J190" t="n">
-        <v>-18.528</v>
+        <v>-16.863</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.6149</v>
       </c>
       <c r="J191" t="n">
-        <v>-20.034</v>
+        <v>-18.447</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.39</v>
       </c>
       <c r="I192" t="n">
-        <v>0.9847</v>
+        <v>0.9831</v>
       </c>
       <c r="J192" t="n">
-        <v>23.6328</v>
+        <v>23.5944</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.36</v>
       </c>
       <c r="I193" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.9236</v>
       </c>
       <c r="J193" t="n">
-        <v>22.0536</v>
+        <v>22.1664</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.13</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3122</v>
+        <v>0.3807</v>
       </c>
       <c r="J194" t="n">
-        <v>7.4928</v>
+        <v>9.136799999999999</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.11</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2562</v>
+        <v>0.3263</v>
       </c>
       <c r="J195" t="n">
-        <v>6.1488</v>
+        <v>7.8312</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.1</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2276</v>
+        <v>0.2983</v>
       </c>
       <c r="J196" t="n">
-        <v>5.4624</v>
+        <v>7.1592</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4074</v>
+        <v>0.4604</v>
       </c>
       <c r="J197" t="n">
-        <v>9.7776</v>
+        <v>11.0496</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0618</v>
       </c>
       <c r="J198" t="n">
-        <v>2.1672</v>
+        <v>1.4832</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.85</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2728</v>
+        <v>-0.1757</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.5472</v>
+        <v>-4.2168</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.77</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3988</v>
+        <v>-0.2558</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.571199999999999</v>
+        <v>-6.1392</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.65</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5644</v>
+        <v>-0.3707</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.5456</v>
+        <v>-8.896800000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.4</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.7997</v>
       </c>
       <c r="J202" t="n">
-        <v>18.3316</v>
+        <v>22.3916</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.09</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2207</v>
+        <v>0.2325</v>
       </c>
       <c r="J203" t="n">
-        <v>6.1796</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.93</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1641</v>
+        <v>-0.0974</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.5948</v>
+        <v>-2.7272</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.8</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3773</v>
+        <v>-0.236</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.5644</v>
+        <v>-6.608</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5798</v>
+        <v>-0.3803</v>
       </c>
       <c r="J206" t="n">
-        <v>-16.2344</v>
+        <v>-10.6484</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.36</v>
       </c>
       <c r="I207" t="n">
-        <v>0.9724</v>
+        <v>0.9568</v>
       </c>
       <c r="J207" t="n">
-        <v>27.2272</v>
+        <v>26.7904</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.12</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3621</v>
+        <v>0.3736</v>
       </c>
       <c r="J208" t="n">
-        <v>10.1388</v>
+        <v>10.4608</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.07</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1908</v>
+        <v>0.2344</v>
       </c>
       <c r="J209" t="n">
-        <v>5.3424</v>
+        <v>6.5632</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.06</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1578</v>
+        <v>0.2039</v>
       </c>
       <c r="J210" t="n">
-        <v>4.4184</v>
+        <v>5.7092</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.98</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1909</v>
+        <v>-0.1235</v>
       </c>
       <c r="J211" t="n">
-        <v>-5.3452</v>
+        <v>-3.458</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.37</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5901</v>
+        <v>0.7146</v>
       </c>
       <c r="J212" t="n">
-        <v>15.3426</v>
+        <v>18.5796</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.27</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4613</v>
+        <v>0.5453</v>
       </c>
       <c r="J213" t="n">
-        <v>11.9938</v>
+        <v>14.1778</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.12</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2388</v>
+        <v>0.2731</v>
       </c>
       <c r="J214" t="n">
-        <v>6.2088</v>
+        <v>7.1006</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.97</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1146</v>
+        <v>-0.0557</v>
       </c>
       <c r="J215" t="n">
-        <v>-2.9796</v>
+        <v>-1.4482</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7009</v>
+        <v>-0.471</v>
       </c>
       <c r="J216" t="n">
-        <v>-18.2234</v>
+        <v>-12.246</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.39</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0403</v>
+        <v>1.0144</v>
       </c>
       <c r="J217" t="n">
-        <v>27.0478</v>
+        <v>26.3744</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.28</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7953</v>
+        <v>0.7748</v>
       </c>
       <c r="J218" t="n">
-        <v>20.6778</v>
+        <v>20.1448</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.2</v>
       </c>
       <c r="I219" t="n">
-        <v>0.599</v>
+        <v>0.5795</v>
       </c>
       <c r="J219" t="n">
-        <v>15.574</v>
+        <v>15.067</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.91</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4184</v>
+        <v>-0.3512</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.8784</v>
+        <v>-9.1312</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.78</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.754</v>
+        <v>-0.7045</v>
       </c>
       <c r="J221" t="n">
-        <v>-19.604</v>
+        <v>-18.317</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.59</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3695</v>
+        <v>1.2402</v>
       </c>
       <c r="J222" t="n">
-        <v>34.2375</v>
+        <v>31.005</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.38</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9406</v>
+        <v>0.9534</v>
       </c>
       <c r="J223" t="n">
-        <v>23.515</v>
+        <v>23.835</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.23</v>
       </c>
       <c r="I224" t="n">
-        <v>0.5555</v>
+        <v>0.6216</v>
       </c>
       <c r="J224" t="n">
-        <v>13.8875</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.19</v>
       </c>
       <c r="I225" t="n">
-        <v>0.4508</v>
+        <v>0.5254</v>
       </c>
       <c r="J225" t="n">
-        <v>11.27</v>
+        <v>13.135</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.91</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4653</v>
+        <v>-0.3888</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.6325</v>
+        <v>-9.720000000000001</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.2</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4324</v>
+        <v>0.4929</v>
       </c>
       <c r="J227" t="n">
-        <v>10.81</v>
+        <v>12.3225</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.95</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0576</v>
+        <v>-0.0621</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.44</v>
+        <v>-1.5525</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.91</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1349</v>
+        <v>-0.1101</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.3725</v>
+        <v>-2.7525</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.64</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5712</v>
+        <v>-0.3764</v>
       </c>
       <c r="J230" t="n">
-        <v>-14.28</v>
+        <v>-9.41</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.63</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.3858</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.605</v>
+        <v>-9.645</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.28</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4933</v>
+        <v>0.5815</v>
       </c>
       <c r="J232" t="n">
-        <v>14.799</v>
+        <v>17.445</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.12</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2606</v>
+        <v>0.286</v>
       </c>
       <c r="J233" t="n">
-        <v>7.818</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.97</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.0502</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.796</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.89</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2454</v>
+        <v>-0.1455</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.362</v>
+        <v>-4.365</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.75</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.454</v>
+        <v>-0.2885</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.62</v>
+        <v>-8.654999999999999</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.47</v>
       </c>
       <c r="I237" t="n">
-        <v>1.1889</v>
+        <v>1.1165</v>
       </c>
       <c r="J237" t="n">
-        <v>35.667</v>
+        <v>33.495</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.38</v>
       </c>
       <c r="I238" t="n">
-        <v>1.0008</v>
+        <v>0.9859</v>
       </c>
       <c r="J238" t="n">
-        <v>30.024</v>
+        <v>29.577</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.16</v>
       </c>
       <c r="I239" t="n">
-        <v>0.4635</v>
+        <v>0.4711</v>
       </c>
       <c r="J239" t="n">
-        <v>13.905</v>
+        <v>14.133</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.87</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5405</v>
+        <v>-0.4747</v>
       </c>
       <c r="J240" t="n">
-        <v>-16.215</v>
+        <v>-14.241</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.85</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5924</v>
+        <v>-0.5295</v>
       </c>
       <c r="J241" t="n">
-        <v>-17.772</v>
+        <v>-15.885</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.14</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2694</v>
+        <v>0.3101</v>
       </c>
       <c r="J242" t="n">
-        <v>11.3148</v>
+        <v>13.0242</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.12</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2363</v>
+        <v>0.2719</v>
       </c>
       <c r="J243" t="n">
-        <v>9.9246</v>
+        <v>11.4198</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.08</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1635</v>
+        <v>0.1929</v>
       </c>
       <c r="J244" t="n">
-        <v>6.867</v>
+        <v>8.101800000000001</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.05</v>
       </c>
       <c r="I245" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.1301</v>
       </c>
       <c r="J245" t="n">
-        <v>3.9564</v>
+        <v>5.4642</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.93</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1943</v>
+        <v>-0.1069</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.160600000000001</v>
+        <v>-4.4898</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.37</v>
       </c>
       <c r="I247" t="n">
-        <v>1.0313</v>
+        <v>1.0022</v>
       </c>
       <c r="J247" t="n">
-        <v>43.3146</v>
+        <v>42.0924</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.22</v>
       </c>
       <c r="I248" t="n">
-        <v>0.6872</v>
+        <v>0.6511</v>
       </c>
       <c r="J248" t="n">
-        <v>28.8624</v>
+        <v>27.3462</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2993</v>
+        <v>-0.2427</v>
       </c>
       <c r="J249" t="n">
-        <v>-12.5706</v>
+        <v>-10.1934</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.91</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3922</v>
+        <v>-0.334</v>
       </c>
       <c r="J250" t="n">
-        <v>-16.4724</v>
+        <v>-14.028</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6615</v>
+        <v>-0.6098</v>
       </c>
       <c r="J251" t="n">
-        <v>-27.783</v>
+        <v>-25.6116</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2110/event_2110_evp_summary.xlsx
+++ b/database/event/2110/event_2110_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6535</v>
+        <v>6.6761</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3164</v>
+        <v>1.3209</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3657</v>
+        <v>2.4149</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6535</v>
+        <v>6.6761</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7285</v>
+        <v>2.6359</v>
       </c>
       <c r="G2" t="n">
-        <v>3.925</v>
+        <v>4.0402</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1271</v>
+        <v>3.8025</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1459</v>
+        <v>2.0533</v>
       </c>
       <c r="J2" t="n">
-        <v>3.925</v>
+        <v>4.0402</v>
       </c>
       <c r="K2" t="n">
         <v>117</v>
@@ -529,7 +529,7 @@
         <v>128</v>
       </c>
       <c r="M2" t="n">
-        <v>6.0709</v>
+        <v>6.0935</v>
       </c>
       <c r="N2" t="n">
         <v>245</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6232</v>
+        <v>6.608</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3105</v>
+        <v>1.3074</v>
       </c>
       <c r="D3" t="n">
-        <v>2.352</v>
+        <v>2.3839</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6232</v>
+        <v>6.608</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3481</v>
+        <v>3.2421</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2751</v>
+        <v>3.3659</v>
       </c>
       <c r="H3" t="n">
-        <v>6.3102</v>
+        <v>5.8029</v>
       </c>
       <c r="I3" t="n">
-        <v>3.281</v>
+        <v>3.1335</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2751</v>
+        <v>3.3659</v>
       </c>
       <c r="K3" t="n">
         <v>117</v>
@@ -575,7 +575,7 @@
         <v>128</v>
       </c>
       <c r="M3" t="n">
-        <v>6.556100000000001</v>
+        <v>6.4994</v>
       </c>
       <c r="N3" t="n">
         <v>245</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.7257</v>
+        <v>3.6644</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7372</v>
+        <v>0.725</v>
       </c>
       <c r="D4" t="n">
-        <v>1.044</v>
+        <v>1.0439</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7257</v>
+        <v>3.6644</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1671</v>
+        <v>3.0345</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5586</v>
+        <v>0.6299</v>
       </c>
       <c r="H4" t="n">
-        <v>5.6726</v>
+        <v>5.1179</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9495</v>
+        <v>2.7636</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5586</v>
+        <v>0.6299</v>
       </c>
       <c r="K4" t="n">
         <v>156</v>
@@ -621,7 +621,7 @@
         <v>78</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5081</v>
+        <v>3.3935</v>
       </c>
       <c r="N4" t="n">
         <v>234</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6524</v>
+        <v>3.6201</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7227</v>
+        <v>0.7163</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0109</v>
+        <v>1.0237</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6524</v>
+        <v>3.6201</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4909</v>
+        <v>3.4132</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1615</v>
+        <v>0.2069</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8133</v>
+        <v>6.3671</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5426</v>
+        <v>3.4382</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1615</v>
+        <v>0.2069</v>
       </c>
       <c r="K5" t="n">
         <v>156</v>
@@ -667,7 +667,7 @@
         <v>78</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7041</v>
+        <v>3.6451</v>
       </c>
       <c r="N5" t="n">
         <v>234</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5601</v>
+        <v>3.5709</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7044</v>
+        <v>0.7065</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9692</v>
+        <v>1.0013</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5601</v>
+        <v>3.5709</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6319</v>
+        <v>2.5224</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9282</v>
+        <v>1.0485</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7869</v>
+        <v>3.4282</v>
       </c>
       <c r="I6" t="n">
-        <v>1.969</v>
+        <v>1.8512</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9282</v>
+        <v>1.0485</v>
       </c>
       <c r="K6" t="n">
         <v>54</v>
@@ -713,7 +713,7 @@
         <v>132</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8972</v>
+        <v>2.8997</v>
       </c>
       <c r="N6" t="n">
         <v>186</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5465</v>
+        <v>3.4974</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7017</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9631</v>
+        <v>0.9679</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5465</v>
+        <v>3.4974</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3447</v>
+        <v>2.2735</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2018</v>
+        <v>1.2239</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7749</v>
+        <v>2.6071</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4428</v>
+        <v>1.4078</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2018</v>
+        <v>1.2239</v>
       </c>
       <c r="K7" t="n">
         <v>54</v>
@@ -759,7 +759,7 @@
         <v>132</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6446</v>
+        <v>2.6317</v>
       </c>
       <c r="N7" t="n">
         <v>186</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2044</v>
+        <v>3.1663</v>
       </c>
       <c r="C8" t="n">
-        <v>0.634</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8086</v>
+        <v>0.8172</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2044</v>
+        <v>3.1663</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4187</v>
+        <v>2.3232</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7857</v>
+        <v>0.8431</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0357</v>
+        <v>2.7708</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5784</v>
+        <v>1.4962</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7857</v>
+        <v>0.8431</v>
       </c>
       <c r="K8" t="n">
         <v>53</v>
@@ -805,7 +805,7 @@
         <v>74</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3641</v>
+        <v>2.3393</v>
       </c>
       <c r="N8" t="n">
         <v>127</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2035</v>
+        <v>2.9823</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6338</v>
+        <v>0.5901</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8082</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2035</v>
+        <v>2.9823</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9923</v>
+        <v>1.7456</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2112</v>
+        <v>1.2367</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9923</v>
+        <v>1.7456</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0359</v>
+        <v>0.9426</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2112</v>
+        <v>1.2367</v>
       </c>
       <c r="K9" t="n">
         <v>117</v>
@@ -851,7 +851,7 @@
         <v>128</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2471</v>
+        <v>2.1793</v>
       </c>
       <c r="N9" t="n">
         <v>245</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9618</v>
+        <v>2.6545</v>
       </c>
       <c r="C10" t="n">
-        <v>0.586</v>
+        <v>0.5252</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9618</v>
+        <v>2.6545</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9618</v>
+        <v>2.6545</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1439</v>
+        <v>3.0849</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2732</v>
+        <v>3.1644</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2732</v>
+        <v>3.1644</v>
       </c>
       <c r="N10" t="n">
         <v>143</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8611</v>
+        <v>2.5414</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5661</v>
+        <v>0.5028</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6536</v>
+        <v>0.5327</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8611</v>
+        <v>2.5414</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8611</v>
+        <v>2.5414</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9228</v>
+        <v>2.8374</v>
       </c>
       <c r="I11" t="n">
-        <v>3.043</v>
+        <v>2.9105</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.043</v>
+        <v>2.9105</v>
       </c>
       <c r="N11" t="n">
         <v>200</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4024</v>
+        <v>2.4899</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4753</v>
+        <v>0.4926</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4465</v>
+        <v>0.5093</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4024</v>
+        <v>2.4899</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4259</v>
+        <v>1.4445</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9765</v>
+        <v>1.0454</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4259</v>
+        <v>1.4445</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9765</v>
+        <v>1.0454</v>
       </c>
       <c r="K12" t="n">
         <v>117</v>
@@ -989,7 +989,7 @@
         <v>128</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7179</v>
+        <v>1.8254</v>
       </c>
       <c r="N12" t="n">
         <v>245</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1868</v>
+        <v>2.1122</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4327</v>
+        <v>0.4179</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3492</v>
+        <v>0.3373</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1868</v>
+        <v>2.1122</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3454</v>
+        <v>2.2838</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1586</v>
+        <v>-0.1716</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7774</v>
+        <v>2.6408</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4441</v>
+        <v>1.426</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1586</v>
+        <v>-0.1716</v>
       </c>
       <c r="K13" t="n">
         <v>53</v>
@@ -1035,7 +1035,7 @@
         <v>74</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2855</v>
+        <v>1.2544</v>
       </c>
       <c r="N13" t="n">
         <v>127</v>
@@ -1044,185 +1044,185 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>znajder</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0761</v>
+        <v>2.1077</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4108</v>
+        <v>0.417</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2992</v>
+        <v>0.3353</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0761</v>
+        <v>2.1077</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6382</v>
+        <v>1.4043</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4379</v>
+        <v>0.7034</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6382</v>
+        <v>1.4043</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8518</v>
+        <v>0.7583</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4379</v>
+        <v>0.7034</v>
       </c>
       <c r="K14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L14" t="n">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2897</v>
+        <v>1.4617</v>
       </c>
       <c r="N14" t="n">
-        <v>186</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>znajder</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.048</v>
+        <v>2.0681</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4052</v>
+        <v>0.4092</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2866</v>
+        <v>0.3172</v>
       </c>
       <c r="E15" t="n">
-        <v>2.048</v>
+        <v>2.0681</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4613</v>
+        <v>1.5658</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5867</v>
+        <v>0.5023</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4613</v>
+        <v>1.5658</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7598</v>
+        <v>0.8455</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5867</v>
+        <v>0.5023</v>
       </c>
       <c r="K15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L15" t="n">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3465</v>
+        <v>1.3478</v>
       </c>
       <c r="N15" t="n">
-        <v>127</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9918</v>
+        <v>1.9333</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3941</v>
+        <v>0.3825</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2612</v>
+        <v>0.2559</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9918</v>
+        <v>1.9333</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9918</v>
+        <v>0.5356</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.3977</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9918</v>
+        <v>0.5356</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0737</v>
+        <v>0.2892</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.3977</v>
       </c>
       <c r="K16" t="n">
-        <v>200</v>
+        <v>117</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0737</v>
+        <v>1.6869</v>
       </c>
       <c r="N16" t="n">
-        <v>200</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9663</v>
+        <v>1.911</v>
       </c>
       <c r="C17" t="n">
-        <v>0.389</v>
+        <v>0.3781</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2497</v>
+        <v>0.2457</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9663</v>
+        <v>1.911</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6647</v>
+        <v>1.911</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3016</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6647</v>
+        <v>1.911</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3456</v>
+        <v>1.9602</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3016</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="L17" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6472</v>
+        <v>1.9602</v>
       </c>
       <c r="N17" t="n">
-        <v>245</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8154</v>
+        <v>1.7951</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3592</v>
+        <v>0.3552</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1815</v>
+        <v>0.193</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8154</v>
+        <v>1.7951</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8154</v>
+        <v>1.7951</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8154</v>
+        <v>1.7951</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8901</v>
+        <v>1.8414</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8901</v>
+        <v>1.8414</v>
       </c>
       <c r="N18" t="n">
         <v>143</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5524</v>
+        <v>1.4401</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3072</v>
+        <v>0.2849</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0314</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5524</v>
+        <v>1.4401</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2815</v>
+        <v>2.1965</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7291</v>
+        <v>-0.7564</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5521</v>
+        <v>2.353</v>
       </c>
       <c r="I19" t="n">
-        <v>1.327</v>
+        <v>1.2706</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7291</v>
+        <v>-0.7564</v>
       </c>
       <c r="K19" t="n">
         <v>53</v>
@@ -1311,7 +1311,7 @@
         <v>74</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5979</v>
+        <v>0.5142</v>
       </c>
       <c r="N19" t="n">
         <v>127</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4085</v>
+        <v>1.3692</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2787</v>
+        <v>0.2709</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0021</v>
+        <v>-0.0009</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4085</v>
+        <v>1.3692</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4085</v>
+        <v>1.3692</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4085</v>
+        <v>1.3692</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4664</v>
+        <v>1.4045</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4664</v>
+        <v>1.4045</v>
       </c>
       <c r="N20" t="n">
         <v>143</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2687</v>
+        <v>1.283</v>
       </c>
       <c r="C21" t="n">
-        <v>0.251</v>
+        <v>0.2539</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0653</v>
+        <v>-0.0402</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2687</v>
+        <v>1.283</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2687</v>
+        <v>1.283</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2687</v>
+        <v>1.283</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2687</v>
+        <v>1.283</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2687</v>
+        <v>1.283</v>
       </c>
       <c r="N21" t="n">
         <v>131</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2443</v>
+        <v>1.2349</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2462</v>
+        <v>0.2443</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.0621</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2443</v>
+        <v>1.2349</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2443</v>
+        <v>1.2349</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2443</v>
+        <v>1.2349</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2443</v>
+        <v>1.2349</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2443</v>
+        <v>1.2349</v>
       </c>
       <c r="N22" t="n">
         <v>131</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0924</v>
+        <v>1.0506</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2161</v>
+        <v>0.2079</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1449</v>
+        <v>-0.1459</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0924</v>
+        <v>1.0506</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0924</v>
+        <v>1.0506</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0924</v>
+        <v>1.0506</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0924</v>
+        <v>1.0506</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0924</v>
+        <v>1.0506</v>
       </c>
       <c r="N23" t="n">
         <v>131</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0485</v>
+        <v>1.0478</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2075</v>
+        <v>0.2073</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1647</v>
+        <v>-0.1472</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0485</v>
+        <v>1.0478</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0485</v>
+        <v>1.0478</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0485</v>
+        <v>1.0478</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0916</v>
+        <v>1.0748</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0916</v>
+        <v>1.0748</v>
       </c>
       <c r="N24" t="n">
         <v>143</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0154</v>
+        <v>0.9718</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2009</v>
+        <v>0.1923</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1796</v>
+        <v>-0.1818</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0154</v>
+        <v>0.9718</v>
       </c>
       <c r="F25" t="n">
-        <v>0.881</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1344</v>
+        <v>0.1457</v>
       </c>
       <c r="H25" t="n">
-        <v>0.881</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4581</v>
+        <v>0.4461</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1344</v>
+        <v>0.1457</v>
       </c>
       <c r="K25" t="n">
         <v>156</v>
@@ -1587,7 +1587,7 @@
         <v>78</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5925</v>
+        <v>0.5918</v>
       </c>
       <c r="N25" t="n">
         <v>234</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8928</v>
+        <v>0.9472</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1766</v>
+        <v>0.1874</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.235</v>
+        <v>-0.193</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8928</v>
+        <v>0.9472</v>
       </c>
       <c r="F26" t="n">
-        <v>0.507</v>
+        <v>0.4657</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3858</v>
+        <v>0.4815</v>
       </c>
       <c r="H26" t="n">
-        <v>0.507</v>
+        <v>0.4657</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2636</v>
+        <v>0.2515</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3858</v>
+        <v>0.4815</v>
       </c>
       <c r="K26" t="n">
         <v>156</v>
@@ -1633,7 +1633,7 @@
         <v>78</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6494</v>
+        <v>0.733</v>
       </c>
       <c r="N26" t="n">
         <v>234</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6704</v>
+        <v>0.5941</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1326</v>
+        <v>0.1175</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3354</v>
+        <v>-0.3538</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6704</v>
+        <v>0.5941</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6704</v>
+        <v>0.5941</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6704</v>
+        <v>0.5941</v>
       </c>
       <c r="I27" t="n">
-        <v>0.698</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.698</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="N27" t="n">
         <v>143</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5746</v>
+        <v>0.5578</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1137</v>
+        <v>0.1104</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3786</v>
+        <v>-0.3703</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5746</v>
+        <v>0.5578</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5746</v>
+        <v>0.5578</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5746</v>
+        <v>0.5578</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5746</v>
+        <v>0.5578</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.5746</v>
+        <v>0.5578</v>
       </c>
       <c r="N28" t="n">
         <v>72</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4399</v>
+        <v>0.4129</v>
       </c>
       <c r="C29" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4394</v>
+        <v>-0.4362</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4399</v>
+        <v>0.4129</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4399</v>
+        <v>0.4129</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4399</v>
+        <v>0.4129</v>
       </c>
       <c r="I29" t="n">
-        <v>0.458</v>
+        <v>0.4235</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.458</v>
+        <v>0.4235</v>
       </c>
       <c r="N29" t="n">
         <v>200</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3744</v>
+        <v>0.3244</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0741</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.469</v>
+        <v>-0.4765</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3744</v>
+        <v>0.3244</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3744</v>
+        <v>0.3244</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3744</v>
+        <v>0.3244</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3898</v>
+        <v>0.3328</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3898</v>
+        <v>0.3328</v>
       </c>
       <c r="N30" t="n">
         <v>200</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3051</v>
+        <v>0.2565</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0604</v>
+        <v>0.0508</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5003</v>
+        <v>-0.5074</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3051</v>
+        <v>0.2565</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3051</v>
+        <v>0.2565</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3051</v>
+        <v>0.2565</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3051</v>
+        <v>0.2565</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.3051</v>
+        <v>0.2565</v>
       </c>
       <c r="N31" t="n">
         <v>72</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2112</v>
+        <v>0.1516</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0418</v>
+        <v>0.03</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5427</v>
+        <v>-0.5552</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2112</v>
+        <v>0.1516</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2112</v>
+        <v>0.1516</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2112</v>
+        <v>0.1516</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2112</v>
+        <v>0.1516</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2112</v>
+        <v>0.1516</v>
       </c>
       <c r="N32" t="n">
         <v>72</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1479</v>
+        <v>0.1025</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0293</v>
+        <v>0.0203</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5712</v>
+        <v>-0.5775</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1479</v>
+        <v>0.1025</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1479</v>
+        <v>0.1025</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1479</v>
+        <v>0.1025</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1479</v>
+        <v>0.1025</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1479</v>
+        <v>0.1025</v>
       </c>
       <c r="N33" t="n">
         <v>72</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1085</v>
+        <v>0.0757</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0215</v>
+        <v>0.015</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.589</v>
+        <v>-0.5897</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1085</v>
+        <v>0.0757</v>
       </c>
       <c r="F34" t="n">
-        <v>0.758</v>
+        <v>0.6869</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.6495</v>
+        <v>-0.6112</v>
       </c>
       <c r="H34" t="n">
-        <v>0.758</v>
+        <v>0.6869</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3941</v>
+        <v>0.3709</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.6495</v>
+        <v>-0.6112</v>
       </c>
       <c r="K34" t="n">
         <v>54</v>
@@ -2001,7 +2001,7 @@
         <v>132</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2554</v>
+        <v>-0.2403</v>
       </c>
       <c r="N34" t="n">
         <v>186</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.2922</v>
+        <v>-0.1061</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0578</v>
+        <v>-0.021</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7699</v>
+        <v>-0.6725</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.2922</v>
+        <v>-0.1061</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3393</v>
+        <v>-0.2606</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0471</v>
+        <v>0.1545</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3393</v>
+        <v>-0.2606</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1764</v>
+        <v>-0.1407</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0471</v>
+        <v>0.1545</v>
       </c>
       <c r="K35" t="n">
         <v>54</v>
@@ -2047,7 +2047,7 @@
         <v>132</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.1293</v>
+        <v>0.01380000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>186</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5502</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1089</v>
+        <v>-0.1096</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8864</v>
+        <v>-0.8763</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5502</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5502</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5502</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5502</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5502</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="N36" t="n">
         <v>131</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.5664</v>
+        <v>-0.5794</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1121</v>
+        <v>-0.1146</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8937</v>
+        <v>-0.888</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.5664</v>
+        <v>-0.5794</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.5664</v>
+        <v>-0.5794</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5664</v>
+        <v>-0.5794</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.5664</v>
+        <v>-0.5794</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.5664</v>
+        <v>-0.5794</v>
       </c>
       <c r="N37" t="n">
         <v>131</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.4308</v>
+        <v>-1.3573</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2831</v>
+        <v>-0.2686</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2839</v>
+        <v>-1.2421</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4308</v>
+        <v>-1.3573</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9853</v>
+        <v>-0.8954</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.4455</v>
+        <v>-0.4619</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9853</v>
+        <v>-0.8954</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.5123</v>
+        <v>-0.4835</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.4455</v>
+        <v>-0.4619</v>
       </c>
       <c r="K38" t="n">
         <v>53</v>
@@ -2185,7 +2185,7 @@
         <v>74</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9578</v>
+        <v>-0.9454</v>
       </c>
       <c r="N38" t="n">
         <v>127</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.471</v>
+        <v>-1.4762</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.291</v>
+        <v>-0.2921</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3021</v>
+        <v>-1.2962</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.471</v>
+        <v>-1.4762</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.471</v>
+        <v>-1.4762</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.471</v>
+        <v>-1.4762</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.471</v>
+        <v>-1.4762</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.471</v>
+        <v>-1.4762</v>
       </c>
       <c r="N39" t="n">
         <v>72</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9075</v>
+        <v>-1.863</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3774</v>
+        <v>-0.3686</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4992</v>
+        <v>-1.4723</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9075</v>
+        <v>-1.863</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.9075</v>
+        <v>-1.863</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.9075</v>
+        <v>-1.863</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.986</v>
+        <v>-1.911</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.986</v>
+        <v>-1.911</v>
       </c>
       <c r="N40" t="n">
         <v>200</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4976</v>
+        <v>-2.3558</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4942</v>
+        <v>-0.4661</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7656</v>
+        <v>-1.6966</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4976</v>
+        <v>-2.3558</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.3993</v>
+        <v>-2.2243</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0983</v>
+        <v>-0.1315</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.3993</v>
+        <v>-2.2243</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.2475</v>
+        <v>-1.2011</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.0983</v>
+        <v>-0.1315</v>
       </c>
       <c r="K41" t="n">
         <v>156</v>
@@ -2323,7 +2323,7 @@
         <v>78</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.3458</v>
+        <v>-1.3326</v>
       </c>
       <c r="N41" t="n">
         <v>234</v>
@@ -2429,10 +2429,10 @@
         <v>1.57</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0546</v>
+        <v>1.0184</v>
       </c>
       <c r="J2" t="n">
-        <v>29.5288</v>
+        <v>28.5152</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.92</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1069</v>
+        <v>-0.12</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.9932</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.86</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1721</v>
+        <v>-0.1868</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.8188</v>
+        <v>-5.2304</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.85</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1826</v>
+        <v>-0.1973</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.1128</v>
+        <v>-5.5244</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.57</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4518</v>
+        <v>-0.4595</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.6504</v>
+        <v>-12.866</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.45</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0725</v>
+        <v>1.0405</v>
       </c>
       <c r="J7" t="n">
-        <v>30.03</v>
+        <v>29.134</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0.9455</v>
       </c>
       <c r="J8" t="n">
-        <v>28</v>
+        <v>26.474</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.31</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.7694</v>
       </c>
       <c r="J9" t="n">
-        <v>22.708</v>
+        <v>21.5432</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.98</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1497</v>
+        <v>-0.1384</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.1916</v>
+        <v>-3.8752</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.96</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.222</v>
+        <v>-0.2089</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.216</v>
+        <v>-5.8492</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.08</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2723</v>
+        <v>0.2617</v>
       </c>
       <c r="J12" t="n">
-        <v>7.0798</v>
+        <v>6.8042</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.88</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1354</v>
+        <v>-0.1534</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.5204</v>
+        <v>-3.9884</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.83</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1877</v>
+        <v>-0.2061</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.8802</v>
+        <v>-5.3586</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.66</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3498</v>
+        <v>-0.3652</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.094799999999999</v>
+        <v>-9.495200000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.6</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4061</v>
+        <v>-0.419</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.5586</v>
+        <v>-10.894</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.49</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1042</v>
+        <v>1.092</v>
       </c>
       <c r="J17" t="n">
-        <v>28.7092</v>
+        <v>28.392</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.44</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0407</v>
+        <v>1.0007</v>
       </c>
       <c r="J18" t="n">
-        <v>27.0582</v>
+        <v>26.0182</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.29</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7487</v>
+        <v>0.7178</v>
       </c>
       <c r="J19" t="n">
-        <v>19.4662</v>
+        <v>18.6628</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.24</v>
       </c>
       <c r="I20" t="n">
-        <v>0.634</v>
+        <v>0.6159</v>
       </c>
       <c r="J20" t="n">
-        <v>16.484</v>
+        <v>16.0134</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.13</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3578</v>
+        <v>0.3672</v>
       </c>
       <c r="J21" t="n">
-        <v>9.3028</v>
+        <v>9.5472</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.95</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0153</v>
+        <v>-0.0389</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3213</v>
+        <v>-0.8169</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.71</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2853</v>
+        <v>-0.3063</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.9913</v>
+        <v>-6.4323</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.67</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3213</v>
+        <v>-0.3414</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.7473</v>
+        <v>-7.1694</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.54</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4413</v>
+        <v>-0.4557</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.267300000000001</v>
+        <v>-9.569699999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.51</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4694</v>
+        <v>-0.4821</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.8574</v>
+        <v>-10.1241</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.86</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2288</v>
+        <v>1.3532</v>
       </c>
       <c r="J27" t="n">
-        <v>25.8048</v>
+        <v>28.4172</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.8</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1614</v>
+        <v>1.282</v>
       </c>
       <c r="J28" t="n">
-        <v>24.3894</v>
+        <v>26.922</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.46</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7716</v>
+        <v>0.8628</v>
       </c>
       <c r="J29" t="n">
-        <v>16.2036</v>
+        <v>18.1188</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.26</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5139</v>
+        <v>0.5792</v>
       </c>
       <c r="J30" t="n">
-        <v>10.7919</v>
+        <v>12.1632</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.23</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4719</v>
+        <v>0.5323</v>
       </c>
       <c r="J31" t="n">
-        <v>9.9099</v>
+        <v>11.1783</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.53</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5195</v>
+        <v>0.5948</v>
       </c>
       <c r="J32" t="n">
-        <v>12.468</v>
+        <v>14.2752</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.47</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4812</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>11.5488</v>
+        <v>13.1976</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2289</v>
+        <v>0.2478</v>
       </c>
       <c r="J34" t="n">
-        <v>5.4936</v>
+        <v>5.9472</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0555</v>
+        <v>0.0722</v>
       </c>
       <c r="J35" t="n">
-        <v>1.332</v>
+        <v>1.7328</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.98</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0591</v>
+        <v>-0.0606</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.4184</v>
+        <v>-1.4544</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.19</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3506</v>
+        <v>0.357</v>
       </c>
       <c r="J37" t="n">
-        <v>8.414400000000001</v>
+        <v>8.568</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.89</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1321</v>
+        <v>-0.1482</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.1704</v>
+        <v>-3.5568</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.86</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1628</v>
+        <v>-0.1796</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.9072</v>
+        <v>-4.3104</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.78</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2423</v>
+        <v>-0.2592</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.8152</v>
+        <v>-6.2208</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4044</v>
+        <v>-0.4161</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.7056</v>
+        <v>-9.9864</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.35</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5468</v>
+        <v>0.6092</v>
       </c>
       <c r="J42" t="n">
-        <v>15.8572</v>
+        <v>17.6668</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.12</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2815</v>
+        <v>0.2872</v>
       </c>
       <c r="J43" t="n">
-        <v>8.163500000000001</v>
+        <v>8.328799999999999</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.93</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1022</v>
+        <v>-0.1131</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.9638</v>
+        <v>-3.2799</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.86</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1797</v>
+        <v>-0.1927</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.2113</v>
+        <v>-5.5883</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.84</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2006</v>
+        <v>-0.2137</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.8174</v>
+        <v>-6.1973</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.42</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7915</v>
+        <v>0.8694</v>
       </c>
       <c r="J47" t="n">
-        <v>22.9535</v>
+        <v>25.2126</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.19</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4674</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>13.5546</v>
+        <v>14.8944</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.11</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3433</v>
+        <v>0.3501</v>
       </c>
       <c r="J49" t="n">
-        <v>9.9557</v>
+        <v>10.1529</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.98</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1166</v>
+        <v>-0.1153</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.3814</v>
+        <v>-3.3437</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.76</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.75</v>
+        <v>-0.6965</v>
       </c>
       <c r="J51" t="n">
-        <v>-21.75</v>
+        <v>-20.1985</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.04</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1152</v>
+        <v>0.1172</v>
       </c>
       <c r="J52" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.95</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0634</v>
+        <v>-0.0765</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.585</v>
+        <v>-1.9125</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.91</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.111</v>
+        <v>-0.1263</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.775</v>
+        <v>-3.1575</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.89</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1329</v>
+        <v>-0.1488</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.3225</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.58</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4333</v>
+        <v>-0.4434</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.8325</v>
+        <v>-11.085</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.51</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5023</v>
+        <v>0.5756</v>
       </c>
       <c r="J57" t="n">
-        <v>12.5575</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.48</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4833</v>
+        <v>0.5534</v>
       </c>
       <c r="J58" t="n">
-        <v>12.0825</v>
+        <v>13.835</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.4</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4323</v>
+        <v>0.4929</v>
       </c>
       <c r="J59" t="n">
-        <v>10.8075</v>
+        <v>12.3225</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.12</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1709</v>
+        <v>0.1913</v>
       </c>
       <c r="J60" t="n">
-        <v>4.2725</v>
+        <v>4.7825</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.88</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1843</v>
+        <v>-0.1914</v>
       </c>
       <c r="J61" t="n">
-        <v>-4.6075</v>
+        <v>-4.785</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.62</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9774</v>
+        <v>1.0817</v>
       </c>
       <c r="J62" t="n">
-        <v>22.4802</v>
+        <v>24.8791</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.47</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7963</v>
+        <v>0.8867</v>
       </c>
       <c r="J63" t="n">
-        <v>18.3149</v>
+        <v>20.3941</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.43</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7473</v>
+        <v>0.8334</v>
       </c>
       <c r="J64" t="n">
-        <v>17.1879</v>
+        <v>19.1682</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.32</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6109</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>14.0507</v>
+        <v>15.709</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.07</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1725</v>
+        <v>0.1991</v>
       </c>
       <c r="J66" t="n">
-        <v>3.9675</v>
+        <v>4.5793</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.33</v>
+        <v>0.3162</v>
       </c>
       <c r="J67" t="n">
-        <v>7.59</v>
+        <v>7.2726</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.78</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2325</v>
+        <v>-0.2516</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.3475</v>
+        <v>-5.7868</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.76</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.251</v>
+        <v>-0.27</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.773</v>
+        <v>-6.21</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.75</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2604</v>
+        <v>-0.2792</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.9892</v>
+        <v>-6.4216</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.51</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4855</v>
+        <v>-0.4948</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.1665</v>
+        <v>-11.3804</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.33</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6826</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="J72" t="n">
-        <v>20.478</v>
+        <v>22.455</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.27</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5967</v>
+        <v>0.6546</v>
       </c>
       <c r="J73" t="n">
-        <v>17.901</v>
+        <v>19.638</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2399</v>
+        <v>-0.2379</v>
       </c>
       <c r="J74" t="n">
-        <v>-7.197</v>
+        <v>-7.137</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.92</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3014</v>
+        <v>-0.2955</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.042</v>
+        <v>-8.865</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.74</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.786</v>
+        <v>-0.7306</v>
       </c>
       <c r="J76" t="n">
-        <v>-23.58</v>
+        <v>-21.918</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.2</v>
       </c>
       <c r="I77" t="n">
-        <v>0.388</v>
+        <v>0.4229</v>
       </c>
       <c r="J77" t="n">
-        <v>11.64</v>
+        <v>12.687</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.19</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3773</v>
+        <v>0.407</v>
       </c>
       <c r="J78" t="n">
-        <v>11.319</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.08</v>
       </c>
       <c r="I79" t="n">
-        <v>0.196</v>
+        <v>0.206</v>
       </c>
       <c r="J79" t="n">
-        <v>5.88</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.95</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0804</v>
+        <v>-0.0895</v>
       </c>
       <c r="J80" t="n">
-        <v>-2.412</v>
+        <v>-2.685</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.244</v>
+        <v>-0.2563</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.32</v>
+        <v>-7.689</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.01</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1175</v>
+        <v>0.1004</v>
       </c>
       <c r="J82" t="n">
-        <v>2.585</v>
+        <v>2.2088</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.78</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2204</v>
+        <v>-0.2423</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.8488</v>
+        <v>-5.3306</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.61</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3796</v>
+        <v>-0.3967</v>
       </c>
       <c r="J84" t="n">
-        <v>-8.3512</v>
+        <v>-8.727399999999999</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.61</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3796</v>
+        <v>-0.3967</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.3512</v>
+        <v>-8.727399999999999</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.48</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5011</v>
+        <v>-0.5113</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.0242</v>
+        <v>-11.2486</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.94</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0147</v>
+        <v>1.0009</v>
       </c>
       <c r="J87" t="n">
-        <v>22.3234</v>
+        <v>22.0198</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.61</v>
       </c>
       <c r="I88" t="n">
-        <v>0.705</v>
+        <v>0.7066</v>
       </c>
       <c r="J88" t="n">
-        <v>15.51</v>
+        <v>15.5452</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.3</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3806</v>
+        <v>0.3993</v>
       </c>
       <c r="J89" t="n">
-        <v>8.373200000000001</v>
+        <v>8.784599999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.15</v>
       </c>
       <c r="I90" t="n">
-        <v>0.198</v>
+        <v>0.2214</v>
       </c>
       <c r="J90" t="n">
-        <v>4.356</v>
+        <v>4.8708</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.98</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.0731</v>
+        <v>-0.0716</v>
       </c>
       <c r="J91" t="n">
-        <v>-1.6082</v>
+        <v>-1.5752</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>1.6427</v>
+        <v>1.6503</v>
       </c>
       <c r="J92" t="n">
-        <v>29.5686</v>
+        <v>29.7054</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.83</v>
       </c>
       <c r="I93" t="n">
-        <v>1.4563</v>
+        <v>1.454</v>
       </c>
       <c r="J93" t="n">
-        <v>26.2134</v>
+        <v>26.172</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.58</v>
       </c>
       <c r="I94" t="n">
-        <v>1.1784</v>
+        <v>1.1563</v>
       </c>
       <c r="J94" t="n">
-        <v>21.2112</v>
+        <v>20.8134</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.44</v>
       </c>
       <c r="I95" t="n">
-        <v>1.0067</v>
+        <v>0.9644</v>
       </c>
       <c r="J95" t="n">
-        <v>18.1206</v>
+        <v>17.3592</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.15</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3527</v>
+        <v>0.3747</v>
       </c>
       <c r="J96" t="n">
-        <v>6.3486</v>
+        <v>6.7446</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4833</v>
+        <v>0.4187</v>
       </c>
       <c r="J97" t="n">
-        <v>8.699400000000001</v>
+        <v>7.5366</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.59</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.3762</v>
+        <v>-0.3975</v>
       </c>
       <c r="J98" t="n">
-        <v>-6.7716</v>
+        <v>-7.155</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.47</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4848</v>
+        <v>-0.4999</v>
       </c>
       <c r="J99" t="n">
-        <v>-8.7264</v>
+        <v>-8.998200000000001</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.38</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5712</v>
+        <v>-0.5797</v>
       </c>
       <c r="J100" t="n">
-        <v>-10.2816</v>
+        <v>-10.4346</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.27</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6787</v>
+        <v>-0.678</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.2166</v>
+        <v>-12.204</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.36</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9352</v>
+        <v>0.8771</v>
       </c>
       <c r="J102" t="n">
-        <v>25.2504</v>
+        <v>23.6817</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.33</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8685</v>
+        <v>0.8175</v>
       </c>
       <c r="J103" t="n">
-        <v>23.4495</v>
+        <v>22.0725</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.26</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7058</v>
+        <v>0.6746</v>
       </c>
       <c r="J104" t="n">
-        <v>19.0566</v>
+        <v>18.2142</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.01</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0113</v>
+        <v>0.0298</v>
       </c>
       <c r="J105" t="n">
-        <v>0.3051</v>
+        <v>0.8046</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2776</v>
+        <v>-0.2642</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.4952</v>
+        <v>-7.1334</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.11</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3029</v>
+        <v>0.2984</v>
       </c>
       <c r="J107" t="n">
-        <v>8.1783</v>
+        <v>8.056800000000001</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.09</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2604</v>
+        <v>0.2579</v>
       </c>
       <c r="J108" t="n">
-        <v>7.0308</v>
+        <v>6.9633</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.89</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.134</v>
+        <v>-0.1496</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.618</v>
+        <v>-4.0392</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.7</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3226</v>
+        <v>-0.337</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.7102</v>
+        <v>-9.099</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.65</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3699</v>
+        <v>-0.3826</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.987299999999999</v>
+        <v>-10.3302</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.08</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1705</v>
+        <v>0.1766</v>
       </c>
       <c r="J112" t="n">
-        <v>5.9675</v>
+        <v>6.181</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.05</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1189</v>
+        <v>0.125</v>
       </c>
       <c r="J113" t="n">
-        <v>4.1615</v>
+        <v>4.375</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0815</v>
+        <v>0.0866</v>
       </c>
       <c r="J114" t="n">
-        <v>2.8525</v>
+        <v>3.031</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.91</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1162</v>
+        <v>-0.1301</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.067</v>
+        <v>-4.5535</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.6</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.422</v>
+        <v>-0.4315</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.77</v>
+        <v>-15.1025</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.33</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4384</v>
+        <v>0.4498</v>
       </c>
       <c r="J117" t="n">
-        <v>15.344</v>
+        <v>15.743</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.21</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2963</v>
+        <v>0.3128</v>
       </c>
       <c r="J118" t="n">
-        <v>10.3705</v>
+        <v>10.948</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.17</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2476</v>
+        <v>0.2648</v>
       </c>
       <c r="J119" t="n">
-        <v>8.666</v>
+        <v>9.268000000000001</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.11</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1696</v>
+        <v>0.1869</v>
       </c>
       <c r="J120" t="n">
-        <v>5.936</v>
+        <v>6.5415</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.03</v>
       </c>
       <c r="I121" t="n">
-        <v>0.0463</v>
+        <v>0.06</v>
       </c>
       <c r="J121" t="n">
-        <v>1.6205</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.36</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.8908</v>
       </c>
       <c r="J122" t="n">
-        <v>27.6399</v>
+        <v>25.8332</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.23</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.621</v>
       </c>
       <c r="J123" t="n">
-        <v>18.8123</v>
+        <v>18.009</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.2</v>
       </c>
       <c r="I124" t="n">
-        <v>0.575</v>
+        <v>0.5553</v>
       </c>
       <c r="J124" t="n">
-        <v>16.675</v>
+        <v>16.1037</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.02</v>
       </c>
       <c r="I125" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0803</v>
       </c>
       <c r="J125" t="n">
-        <v>1.9024</v>
+        <v>2.3287</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5785</v>
+        <v>-0.5425</v>
       </c>
       <c r="J126" t="n">
-        <v>-16.7765</v>
+        <v>-15.7325</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.45</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8549</v>
+        <v>0.8136</v>
       </c>
       <c r="J127" t="n">
-        <v>24.7921</v>
+        <v>23.5944</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.218</v>
+        <v>0.227</v>
       </c>
       <c r="J128" t="n">
-        <v>6.322</v>
+        <v>6.583</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.06</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1551</v>
+        <v>0.1653</v>
       </c>
       <c r="J129" t="n">
-        <v>4.4979</v>
+        <v>4.7937</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0919</v>
+        <v>-0.1019</v>
       </c>
       <c r="J130" t="n">
-        <v>-2.6651</v>
+        <v>-2.9551</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.64</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3962</v>
+        <v>-0.4049</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.4898</v>
+        <v>-11.7421</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.69</v>
       </c>
       <c r="I132" t="n">
-        <v>1.3463</v>
+        <v>1.3282</v>
       </c>
       <c r="J132" t="n">
-        <v>29.6186</v>
+        <v>29.2204</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.42</v>
       </c>
       <c r="I133" t="n">
-        <v>1.0101</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="J133" t="n">
-        <v>22.2222</v>
+        <v>21.1244</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.27</v>
       </c>
       <c r="I134" t="n">
-        <v>0.7020999999999999</v>
+        <v>0.6768</v>
       </c>
       <c r="J134" t="n">
-        <v>15.4462</v>
+        <v>14.8896</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.23</v>
       </c>
       <c r="I135" t="n">
-        <v>0.6087</v>
+        <v>0.5937</v>
       </c>
       <c r="J135" t="n">
-        <v>13.3914</v>
+        <v>13.0614</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.02</v>
       </c>
       <c r="I136" t="n">
-        <v>0.0172</v>
+        <v>0.0465</v>
       </c>
       <c r="J136" t="n">
-        <v>0.3784</v>
+        <v>1.023</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.2</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5144</v>
+        <v>0.4895</v>
       </c>
       <c r="J137" t="n">
-        <v>11.3168</v>
+        <v>10.769</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3089</v>
+        <v>0.2982</v>
       </c>
       <c r="J138" t="n">
-        <v>6.7958</v>
+        <v>6.5604</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0925</v>
+        <v>-0.109</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.035</v>
+        <v>-2.398</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.47</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5282</v>
+        <v>-0.534</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.6204</v>
+        <v>-11.748</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.44</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5555</v>
+        <v>-0.5596</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.221</v>
+        <v>-12.3112</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.59</v>
       </c>
       <c r="I142" t="n">
-        <v>1.223</v>
+        <v>1.1974</v>
       </c>
       <c r="J142" t="n">
-        <v>29.352</v>
+        <v>28.7376</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.54</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1621</v>
+        <v>1.1321</v>
       </c>
       <c r="J143" t="n">
-        <v>27.8904</v>
+        <v>27.1704</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.5</v>
       </c>
       <c r="I144" t="n">
-        <v>1.113</v>
+        <v>1.0792</v>
       </c>
       <c r="J144" t="n">
-        <v>26.712</v>
+        <v>25.9008</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.08</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2119</v>
+        <v>0.2337</v>
       </c>
       <c r="J145" t="n">
-        <v>5.0856</v>
+        <v>5.6088</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.99</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1368</v>
+        <v>-0.1167</v>
       </c>
       <c r="J146" t="n">
-        <v>-3.2832</v>
+        <v>-2.8008</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.12</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3411</v>
+        <v>0.3309</v>
       </c>
       <c r="J147" t="n">
-        <v>8.186400000000001</v>
+        <v>7.9416</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.88</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1407</v>
+        <v>-0.1575</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.3768</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.86</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1615</v>
+        <v>-0.1787</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.876</v>
+        <v>-4.2888</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.83</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1909</v>
+        <v>-0.2085</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.5816</v>
+        <v>-5.004</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.55</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4576</v>
+        <v>-0.4671</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.9824</v>
+        <v>-11.2104</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.61</v>
       </c>
       <c r="I152" t="n">
-        <v>1.2364</v>
+        <v>1.2138</v>
       </c>
       <c r="J152" t="n">
-        <v>27.2008</v>
+        <v>26.7036</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.54</v>
       </c>
       <c r="I153" t="n">
-        <v>1.1526</v>
+        <v>1.1239</v>
       </c>
       <c r="J153" t="n">
-        <v>25.3572</v>
+        <v>24.7258</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.46</v>
       </c>
       <c r="I154" t="n">
-        <v>1.0556</v>
+        <v>1.0151</v>
       </c>
       <c r="J154" t="n">
-        <v>23.2232</v>
+        <v>22.3322</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.45</v>
       </c>
       <c r="I155" t="n">
-        <v>1.0427</v>
+        <v>0.9998</v>
       </c>
       <c r="J155" t="n">
-        <v>22.9394</v>
+        <v>21.9956</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.93</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3589</v>
+        <v>-0.3288</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.8958</v>
+        <v>-7.2336</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.19</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4765</v>
       </c>
       <c r="J157" t="n">
-        <v>11.033</v>
+        <v>10.483</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.96</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0396</v>
+        <v>-0.0543</v>
       </c>
       <c r="J158" t="n">
-        <v>-0.8712</v>
+        <v>-1.1946</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.78</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2359</v>
+        <v>-0.2542</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.1898</v>
+        <v>-5.5924</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.7</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3125</v>
+        <v>-0.3291</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.875</v>
+        <v>-7.2402</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.44</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5541</v>
+        <v>-0.5585</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.1902</v>
+        <v>-12.287</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.29</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6227</v>
+        <v>0.5985</v>
       </c>
       <c r="J162" t="n">
-        <v>18.681</v>
+        <v>17.955</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.17</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4016</v>
+        <v>0.3954</v>
       </c>
       <c r="J163" t="n">
-        <v>12.048</v>
+        <v>11.862</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.96</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.059</v>
+        <v>-0.0693</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.77</v>
+        <v>-2.079</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.95</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="J165" t="n">
-        <v>-2.142</v>
+        <v>-2.478</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.35</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6469</v>
+        <v>-0.6433</v>
       </c>
       <c r="J166" t="n">
-        <v>-19.407</v>
+        <v>-19.299</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.4</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0117</v>
+        <v>0.9546</v>
       </c>
       <c r="J167" t="n">
-        <v>30.351</v>
+        <v>28.638</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.39</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9947</v>
+        <v>0.9361</v>
       </c>
       <c r="J168" t="n">
-        <v>29.841</v>
+        <v>28.083</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.34</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8925999999999999</v>
+        <v>0.8384</v>
       </c>
       <c r="J169" t="n">
-        <v>26.778</v>
+        <v>25.152</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.95</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2443</v>
+        <v>-0.233</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.329</v>
+        <v>-6.99</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6693</v>
+        <v>-0.6213</v>
       </c>
       <c r="J171" t="n">
-        <v>-20.079</v>
+        <v>-18.639</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.4</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5298</v>
+        <v>0.5343</v>
       </c>
       <c r="J172" t="n">
-        <v>15.3642</v>
+        <v>15.4947</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.34</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4601</v>
+        <v>0.4685</v>
       </c>
       <c r="J173" t="n">
-        <v>13.3429</v>
+        <v>13.5865</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3157</v>
+        <v>0.3302</v>
       </c>
       <c r="J174" t="n">
-        <v>9.1553</v>
+        <v>9.575799999999999</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.91</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1356</v>
+        <v>-0.1452</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.9324</v>
+        <v>-4.2108</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.71</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3388</v>
+        <v>-0.348</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.825200000000001</v>
+        <v>-10.092</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.17</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3024</v>
+        <v>0.3061</v>
       </c>
       <c r="J177" t="n">
-        <v>8.769600000000001</v>
+        <v>8.876899999999999</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.11</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2121</v>
+        <v>0.219</v>
       </c>
       <c r="J178" t="n">
-        <v>6.1509</v>
+        <v>6.351</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.01</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0339</v>
+        <v>0.0376</v>
       </c>
       <c r="J179" t="n">
-        <v>0.9831</v>
+        <v>1.0904</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.76</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2741</v>
+        <v>-0.2879</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.9489</v>
+        <v>-8.3491</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.76</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2741</v>
+        <v>-0.2879</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.9489</v>
+        <v>-8.3491</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.3</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6156</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="J182" t="n">
-        <v>18.468</v>
+        <v>17.889</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.26</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5455</v>
+        <v>0.5323</v>
       </c>
       <c r="J183" t="n">
-        <v>16.365</v>
+        <v>15.969</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.02</v>
       </c>
       <c r="I184" t="n">
-        <v>0.0654</v>
+        <v>0.073</v>
       </c>
       <c r="J184" t="n">
-        <v>1.962</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1121</v>
+        <v>-0.124</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.363</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.52</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5019</v>
+        <v>-0.5063</v>
       </c>
       <c r="J186" t="n">
-        <v>-15.057</v>
+        <v>-15.189</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.27</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7678</v>
+        <v>0.7221</v>
       </c>
       <c r="J187" t="n">
-        <v>23.034</v>
+        <v>21.663</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.27</v>
       </c>
       <c r="I188" t="n">
-        <v>0.7678</v>
+        <v>0.7221</v>
       </c>
       <c r="J188" t="n">
-        <v>23.034</v>
+        <v>21.663</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.16</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4906</v>
+        <v>0.4759</v>
       </c>
       <c r="J189" t="n">
-        <v>14.718</v>
+        <v>14.277</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.83</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5621</v>
+        <v>-0.531</v>
       </c>
       <c r="J190" t="n">
-        <v>-16.863</v>
+        <v>-15.93</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6149</v>
+        <v>-0.5782</v>
       </c>
       <c r="J191" t="n">
-        <v>-18.447</v>
+        <v>-17.346</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.39</v>
       </c>
       <c r="I192" t="n">
-        <v>0.9831</v>
+        <v>0.9262</v>
       </c>
       <c r="J192" t="n">
-        <v>23.5944</v>
+        <v>22.2288</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.36</v>
       </c>
       <c r="I193" t="n">
-        <v>0.9236</v>
+        <v>0.8685</v>
       </c>
       <c r="J193" t="n">
-        <v>22.1664</v>
+        <v>20.844</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.13</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3807</v>
+        <v>0.383</v>
       </c>
       <c r="J194" t="n">
-        <v>9.136799999999999</v>
+        <v>9.192</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.11</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3263</v>
+        <v>0.3331</v>
       </c>
       <c r="J195" t="n">
-        <v>7.8312</v>
+        <v>7.9944</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.1</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2983</v>
+        <v>0.3073</v>
       </c>
       <c r="J196" t="n">
-        <v>7.1592</v>
+        <v>7.3752</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4604</v>
+        <v>0.446</v>
       </c>
       <c r="J197" t="n">
-        <v>11.0496</v>
+        <v>10.704</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0618</v>
+        <v>0.0607</v>
       </c>
       <c r="J198" t="n">
-        <v>1.4832</v>
+        <v>1.4568</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.85</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1757</v>
+        <v>-0.192</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.2168</v>
+        <v>-4.608</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.77</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2558</v>
+        <v>-0.2716</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.1392</v>
+        <v>-6.5184</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.65</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3707</v>
+        <v>-0.3832</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.896800000000001</v>
+        <v>-9.1968</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.4</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7997</v>
+        <v>0.7601</v>
       </c>
       <c r="J202" t="n">
-        <v>22.3916</v>
+        <v>21.2828</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.09</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2325</v>
+        <v>0.2375</v>
       </c>
       <c r="J203" t="n">
-        <v>6.51</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.93</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.0974</v>
+        <v>-0.1095</v>
       </c>
       <c r="J204" t="n">
-        <v>-2.7272</v>
+        <v>-3.066</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.8</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.236</v>
+        <v>-0.25</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.608</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3803</v>
+        <v>-0.3907</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.6484</v>
+        <v>-10.9396</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.36</v>
       </c>
       <c r="I207" t="n">
-        <v>0.9568</v>
+        <v>0.8937</v>
       </c>
       <c r="J207" t="n">
-        <v>26.7904</v>
+        <v>25.0236</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.12</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3736</v>
+        <v>0.3719</v>
       </c>
       <c r="J208" t="n">
-        <v>10.4608</v>
+        <v>10.4132</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.07</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2344</v>
+        <v>0.2421</v>
       </c>
       <c r="J209" t="n">
-        <v>6.5632</v>
+        <v>6.7788</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.06</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2039</v>
+        <v>0.2134</v>
       </c>
       <c r="J210" t="n">
-        <v>5.7092</v>
+        <v>5.9752</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.98</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1235</v>
+        <v>-0.1201</v>
       </c>
       <c r="J211" t="n">
-        <v>-3.458</v>
+        <v>-3.3628</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.37</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7146</v>
+        <v>0.6892</v>
       </c>
       <c r="J212" t="n">
-        <v>18.5796</v>
+        <v>17.9192</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.27</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5453</v>
+        <v>0.5354</v>
       </c>
       <c r="J213" t="n">
-        <v>14.1778</v>
+        <v>13.9204</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.12</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2731</v>
+        <v>0.2812</v>
       </c>
       <c r="J214" t="n">
-        <v>7.1006</v>
+        <v>7.3112</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.97</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0557</v>
+        <v>-0.0625</v>
       </c>
       <c r="J215" t="n">
-        <v>-1.4482</v>
+        <v>-1.625</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.471</v>
+        <v>-0.4762</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.246</v>
+        <v>-12.3812</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.39</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0144</v>
+        <v>0.9536</v>
       </c>
       <c r="J217" t="n">
-        <v>26.3744</v>
+        <v>24.7936</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.28</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7748</v>
+        <v>0.7313</v>
       </c>
       <c r="J218" t="n">
-        <v>20.1448</v>
+        <v>19.0138</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.2</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5795</v>
+        <v>0.5584</v>
       </c>
       <c r="J219" t="n">
-        <v>15.067</v>
+        <v>14.5184</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.91</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3512</v>
+        <v>-0.3371</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.1312</v>
+        <v>-8.7646</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.78</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7045</v>
+        <v>-0.6554</v>
       </c>
       <c r="J221" t="n">
-        <v>-18.317</v>
+        <v>-17.0404</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.59</v>
       </c>
       <c r="I222" t="n">
-        <v>1.2402</v>
+        <v>1.2126</v>
       </c>
       <c r="J222" t="n">
-        <v>31.005</v>
+        <v>30.315</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.38</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9534</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="J223" t="n">
-        <v>23.835</v>
+        <v>22.4675</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.23</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6216</v>
+        <v>0.6025</v>
       </c>
       <c r="J224" t="n">
-        <v>15.54</v>
+        <v>15.0625</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.19</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5254</v>
+        <v>0.5162</v>
       </c>
       <c r="J225" t="n">
-        <v>13.135</v>
+        <v>12.905</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.91</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3888</v>
+        <v>-0.3634</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.720000000000001</v>
+        <v>-9.085000000000001</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.2</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4929</v>
+        <v>0.4736</v>
       </c>
       <c r="J227" t="n">
-        <v>12.3225</v>
+        <v>11.84</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.95</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0621</v>
+        <v>-0.0756</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.5525</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.91</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1101</v>
+        <v>-0.1255</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.7525</v>
+        <v>-3.1375</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.64</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3764</v>
+        <v>-0.3893</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.41</v>
+        <v>-9.7325</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.63</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3858</v>
+        <v>-0.3983</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.645</v>
+        <v>-9.9575</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.28</v>
       </c>
       <c r="I232" t="n">
-        <v>0.5815</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J232" t="n">
-        <v>17.445</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.12</v>
       </c>
       <c r="I233" t="n">
-        <v>0.286</v>
+        <v>0.2905</v>
       </c>
       <c r="J233" t="n">
-        <v>8.58</v>
+        <v>8.715</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.97</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0502</v>
+        <v>-0.0583</v>
       </c>
       <c r="J234" t="n">
-        <v>-1.506</v>
+        <v>-1.749</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.89</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1455</v>
+        <v>-0.1584</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.365</v>
+        <v>-4.752</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.75</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2885</v>
+        <v>-0.3011</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.654999999999999</v>
+        <v>-9.032999999999999</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.47</v>
       </c>
       <c r="I237" t="n">
-        <v>1.1165</v>
+        <v>1.0747</v>
       </c>
       <c r="J237" t="n">
-        <v>33.495</v>
+        <v>32.241</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.38</v>
       </c>
       <c r="I238" t="n">
-        <v>0.9859</v>
+        <v>0.925</v>
       </c>
       <c r="J238" t="n">
-        <v>29.577</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.16</v>
       </c>
       <c r="I239" t="n">
-        <v>0.4711</v>
+        <v>0.4625</v>
       </c>
       <c r="J239" t="n">
-        <v>14.133</v>
+        <v>13.875</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.87</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4747</v>
+        <v>-0.448</v>
       </c>
       <c r="J240" t="n">
-        <v>-14.241</v>
+        <v>-13.44</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.85</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5295</v>
+        <v>-0.4976</v>
       </c>
       <c r="J241" t="n">
-        <v>-15.885</v>
+        <v>-14.928</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.14</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3101</v>
+        <v>0.3167</v>
       </c>
       <c r="J242" t="n">
-        <v>13.0242</v>
+        <v>13.3014</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.12</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2719</v>
+        <v>0.2803</v>
       </c>
       <c r="J243" t="n">
-        <v>11.4198</v>
+        <v>11.7726</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.08</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1929</v>
+        <v>0.2038</v>
       </c>
       <c r="J244" t="n">
-        <v>8.101800000000001</v>
+        <v>8.5596</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.05</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1301</v>
+        <v>0.1414</v>
       </c>
       <c r="J245" t="n">
-        <v>5.4642</v>
+        <v>5.9388</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.93</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1069</v>
+        <v>-0.1168</v>
       </c>
       <c r="J246" t="n">
-        <v>-4.4898</v>
+        <v>-4.9056</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.37</v>
       </c>
       <c r="I247" t="n">
-        <v>1.0022</v>
+        <v>0.9355</v>
       </c>
       <c r="J247" t="n">
-        <v>42.0924</v>
+        <v>39.291</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.22</v>
       </c>
       <c r="I248" t="n">
-        <v>0.6511</v>
+        <v>0.618</v>
       </c>
       <c r="J248" t="n">
-        <v>27.3462</v>
+        <v>25.956</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2427</v>
+        <v>-0.2399</v>
       </c>
       <c r="J249" t="n">
-        <v>-10.1934</v>
+        <v>-10.0758</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.91</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.334</v>
+        <v>-0.325</v>
       </c>
       <c r="J250" t="n">
-        <v>-14.028</v>
+        <v>-13.65</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6098</v>
+        <v>-0.5746</v>
       </c>
       <c r="J251" t="n">
-        <v>-25.6116</v>
+        <v>-24.1332</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2110/event_2110_evp_summary.xlsx
+++ b/database/event/2110/event_2110_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6761</v>
+        <v>6.6999</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3209</v>
+        <v>1.3256</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4149</v>
+        <v>2.4463</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6761</v>
+        <v>6.6999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6359</v>
+        <v>2.6635</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0402</v>
+        <v>4.0364</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8025</v>
+        <v>3.5573</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0533</v>
+        <v>1.9973</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0402</v>
+        <v>4.0364</v>
       </c>
       <c r="K2" t="n">
         <v>117</v>
@@ -529,7 +529,7 @@
         <v>128</v>
       </c>
       <c r="M2" t="n">
-        <v>6.0935</v>
+        <v>6.033700000000001</v>
       </c>
       <c r="N2" t="n">
         <v>245</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.608</v>
+        <v>6.5598</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3074</v>
+        <v>1.2979</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3839</v>
+        <v>2.3825</v>
       </c>
       <c r="E3" t="n">
-        <v>6.608</v>
+        <v>6.5598</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2421</v>
+        <v>3.2099</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3659</v>
+        <v>3.3499</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8029</v>
+        <v>5.6089</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1335</v>
+        <v>3.1492</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3659</v>
+        <v>3.3499</v>
       </c>
       <c r="K3" t="n">
         <v>117</v>
@@ -575,7 +575,7 @@
         <v>128</v>
       </c>
       <c r="M3" t="n">
-        <v>6.4994</v>
+        <v>6.4991</v>
       </c>
       <c r="N3" t="n">
         <v>245</v>
@@ -584,185 +584,185 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mouz</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.6644</v>
+        <v>3.6504</v>
       </c>
       <c r="C4" t="n">
-        <v>0.725</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0439</v>
+        <v>1.0571</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6644</v>
+        <v>3.6504</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0345</v>
+        <v>2.5804</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6299</v>
+        <v>1.07</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1179</v>
+        <v>3.2452</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7636</v>
+        <v>1.8221</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6299</v>
+        <v>1.07</v>
       </c>
       <c r="K4" t="n">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="L4" t="n">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3935</v>
+        <v>2.8921</v>
       </c>
       <c r="N4" t="n">
-        <v>234</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6201</v>
+        <v>3.6304</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7163</v>
+        <v>0.7183</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0237</v>
+        <v>1.048</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6201</v>
+        <v>3.6304</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4132</v>
+        <v>2.3725</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2069</v>
+        <v>1.2579</v>
       </c>
       <c r="H5" t="n">
-        <v>6.3671</v>
+        <v>2.4648</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4382</v>
+        <v>1.3839</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2069</v>
+        <v>1.2579</v>
       </c>
       <c r="K5" t="n">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="L5" t="n">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6451</v>
+        <v>2.6418</v>
       </c>
       <c r="N5" t="n">
-        <v>234</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>mouz</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5709</v>
+        <v>3.553</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7065</v>
+        <v>0.703</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0013</v>
+        <v>1.0128</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5709</v>
+        <v>3.553</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5224</v>
+        <v>3.0104</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0485</v>
+        <v>0.5426</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4282</v>
+        <v>4.8596</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8512</v>
+        <v>2.7285</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0485</v>
+        <v>0.5426</v>
       </c>
       <c r="K6" t="n">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="L6" t="n">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8997</v>
+        <v>3.2711</v>
       </c>
       <c r="N6" t="n">
-        <v>186</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4974</v>
+        <v>3.493</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6911</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9679</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4974</v>
+        <v>3.493</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2735</v>
+        <v>3.288</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2239</v>
+        <v>0.205</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6071</v>
+        <v>5.902</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4078</v>
+        <v>3.3138</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2239</v>
+        <v>0.205</v>
       </c>
       <c r="K7" t="n">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="L7" t="n">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6317</v>
+        <v>3.5188</v>
       </c>
       <c r="N7" t="n">
-        <v>186</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1663</v>
+        <v>3.1762</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6284</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8172</v>
+        <v>0.8411</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1663</v>
+        <v>3.1762</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3232</v>
+        <v>2.4027</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8431</v>
+        <v>0.7735</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7708</v>
+        <v>2.5782</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4962</v>
+        <v>1.4476</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8431</v>
+        <v>0.7735</v>
       </c>
       <c r="K8" t="n">
         <v>53</v>
@@ -805,7 +805,7 @@
         <v>74</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3393</v>
+        <v>2.2211</v>
       </c>
       <c r="N8" t="n">
         <v>127</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9823</v>
+        <v>2.898</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5901</v>
+        <v>0.5734</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.7144</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9823</v>
+        <v>2.898</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7456</v>
+        <v>1.6519</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2367</v>
+        <v>1.2461</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7456</v>
+        <v>1.6519</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9426</v>
+        <v>0.9275</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2367</v>
+        <v>1.2461</v>
       </c>
       <c r="K9" t="n">
         <v>117</v>
@@ -851,7 +851,7 @@
         <v>128</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1793</v>
+        <v>2.1736</v>
       </c>
       <c r="N9" t="n">
         <v>245</v>
@@ -860,139 +860,139 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6545</v>
+        <v>2.601</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5252</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6545</v>
+        <v>2.601</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6545</v>
+        <v>1.5173</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1.0837</v>
       </c>
       <c r="H10" t="n">
-        <v>3.0849</v>
+        <v>1.5173</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1644</v>
+        <v>0.8519</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.0837</v>
       </c>
       <c r="K10" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1644</v>
+        <v>1.9356</v>
       </c>
       <c r="N10" t="n">
-        <v>143</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5414</v>
+        <v>2.5608</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5028</v>
+        <v>0.5067</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5327</v>
+        <v>0.5608</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5414</v>
+        <v>2.5608</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5414</v>
+        <v>2.5608</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8374</v>
+        <v>2.9184</v>
       </c>
       <c r="I11" t="n">
-        <v>2.9105</v>
+        <v>2.9964</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9105</v>
+        <v>2.9964</v>
       </c>
       <c r="N11" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4899</v>
+        <v>2.436</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4926</v>
+        <v>0.482</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5093</v>
+        <v>0.5039</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4899</v>
+        <v>2.436</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4445</v>
+        <v>2.436</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0454</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4445</v>
+        <v>2.6325</v>
       </c>
       <c r="I12" t="n">
-        <v>0.78</v>
+        <v>2.7028</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0454</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>117</v>
+        <v>200</v>
       </c>
       <c r="L12" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8254</v>
+        <v>2.7028</v>
       </c>
       <c r="N12" t="n">
-        <v>245</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1122</v>
+        <v>2.1987</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4179</v>
+        <v>0.435</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3373</v>
+        <v>0.3958</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1122</v>
+        <v>2.1987</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2838</v>
+        <v>2.3854</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1716</v>
+        <v>-0.1867</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6408</v>
+        <v>2.5131</v>
       </c>
       <c r="I13" t="n">
-        <v>1.426</v>
+        <v>1.411</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1716</v>
+        <v>-0.1867</v>
       </c>
       <c r="K13" t="n">
         <v>53</v>
@@ -1035,7 +1035,7 @@
         <v>74</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2544</v>
+        <v>1.2243</v>
       </c>
       <c r="N13" t="n">
         <v>127</v>
@@ -1044,139 +1044,139 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>znajder</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1077</v>
+        <v>1.8987</v>
       </c>
       <c r="C14" t="n">
-        <v>0.417</v>
+        <v>0.3757</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3353</v>
+        <v>0.2592</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1077</v>
+        <v>1.8987</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4043</v>
+        <v>0.5427</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7034</v>
+        <v>1.356</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4043</v>
+        <v>0.5427</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7583</v>
+        <v>0.3047</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7034</v>
+        <v>1.356</v>
       </c>
       <c r="K14" t="n">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="L14" t="n">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4617</v>
+        <v>1.6607</v>
       </c>
       <c r="N14" t="n">
-        <v>127</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>znajder</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0681</v>
+        <v>1.8821</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4092</v>
+        <v>0.3724</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3172</v>
+        <v>0.2516</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0681</v>
+        <v>1.8821</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5658</v>
+        <v>1.2368</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5023</v>
+        <v>0.6453</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5658</v>
+        <v>1.2368</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8455</v>
+        <v>0.6944</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5023</v>
+        <v>0.6453</v>
       </c>
       <c r="K15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L15" t="n">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3478</v>
+        <v>1.3397</v>
       </c>
       <c r="N15" t="n">
-        <v>186</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9333</v>
+        <v>1.8549</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3825</v>
+        <v>0.367</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2559</v>
+        <v>0.2392</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9333</v>
+        <v>1.8549</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5356</v>
+        <v>1.3794</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3977</v>
+        <v>0.4755</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5356</v>
+        <v>1.3794</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2892</v>
+        <v>0.7745</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3977</v>
+        <v>0.4755</v>
       </c>
       <c r="K16" t="n">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="L16" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6869</v>
+        <v>1.25</v>
       </c>
       <c r="N16" t="n">
-        <v>245</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.911</v>
+        <v>1.8056</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3781</v>
+        <v>0.3573</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2457</v>
+        <v>0.2167</v>
       </c>
       <c r="E17" t="n">
-        <v>1.911</v>
+        <v>1.8056</v>
       </c>
       <c r="F17" t="n">
-        <v>1.911</v>
+        <v>1.8056</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.911</v>
+        <v>1.8056</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9602</v>
+        <v>1.8538</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9602</v>
+        <v>1.8538</v>
       </c>
       <c r="N17" t="n">
         <v>200</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7951</v>
+        <v>1.7412</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3552</v>
+        <v>0.3445</v>
       </c>
       <c r="D18" t="n">
-        <v>0.193</v>
+        <v>0.1874</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7951</v>
+        <v>1.7412</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7951</v>
+        <v>1.7412</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7951</v>
+        <v>1.7412</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8414</v>
+        <v>1.7877</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8414</v>
+        <v>1.7877</v>
       </c>
       <c r="N18" t="n">
         <v>143</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4401</v>
+        <v>1.4491</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2849</v>
+        <v>0.2867</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0314</v>
+        <v>0.0543</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4401</v>
+        <v>1.4491</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1965</v>
+        <v>2.169</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7564</v>
+        <v>-0.7199</v>
       </c>
       <c r="H19" t="n">
-        <v>2.353</v>
+        <v>2.169</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2706</v>
+        <v>1.2178</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7564</v>
+        <v>-0.7199</v>
       </c>
       <c r="K19" t="n">
         <v>53</v>
@@ -1311,7 +1311,7 @@
         <v>74</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5142</v>
+        <v>0.4979</v>
       </c>
       <c r="N19" t="n">
         <v>127</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3692</v>
+        <v>1.3504</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2709</v>
+        <v>0.2672</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0009</v>
+        <v>0.0094</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3692</v>
+        <v>1.3504</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3692</v>
+        <v>1.3504</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3692</v>
+        <v>1.3504</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4045</v>
+        <v>1.3865</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4045</v>
+        <v>1.3865</v>
       </c>
       <c r="N20" t="n">
         <v>143</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.283</v>
+        <v>1.0819</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2539</v>
+        <v>0.2141</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0402</v>
+        <v>-0.1129</v>
       </c>
       <c r="E21" t="n">
-        <v>1.283</v>
+        <v>1.0819</v>
       </c>
       <c r="F21" t="n">
-        <v>1.283</v>
+        <v>1.0819</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.283</v>
+        <v>1.0819</v>
       </c>
       <c r="I21" t="n">
-        <v>1.283</v>
+        <v>1.0819</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.283</v>
+        <v>1.0819</v>
       </c>
       <c r="N21" t="n">
         <v>131</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2349</v>
+        <v>1.0647</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2443</v>
+        <v>0.2107</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0621</v>
+        <v>-0.1208</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2349</v>
+        <v>1.0647</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2349</v>
+        <v>1.0647</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2349</v>
+        <v>1.0647</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2349</v>
+        <v>1.0647</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2349</v>
+        <v>1.0647</v>
       </c>
       <c r="N22" t="n">
         <v>131</v>
@@ -1458,127 +1458,127 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0506</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2079</v>
+        <v>0.1858</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1459</v>
+        <v>-0.178</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0506</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0506</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0506</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0506</v>
+        <v>0.9641</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0506</v>
+        <v>0.9641</v>
       </c>
       <c r="N23" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0478</v>
+        <v>0.9025</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2073</v>
+        <v>0.1786</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1472</v>
+        <v>-0.1947</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0478</v>
+        <v>0.9025</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0478</v>
+        <v>0.9025</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0478</v>
+        <v>0.9025</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0748</v>
+        <v>0.9025</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0748</v>
+        <v>0.9025</v>
       </c>
       <c r="N24" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Furlan</t>
+          <t>SZPERO</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9718</v>
+        <v>0.8248</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1923</v>
+        <v>0.1632</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1818</v>
+        <v>-0.2301</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9718</v>
+        <v>0.8248</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.4328</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1457</v>
+        <v>0.392</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.4328</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4461</v>
+        <v>0.243</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1457</v>
+        <v>0.392</v>
       </c>
       <c r="K25" t="n">
         <v>156</v>
@@ -1587,7 +1587,7 @@
         <v>78</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5918</v>
+        <v>0.635</v>
       </c>
       <c r="N25" t="n">
         <v>234</v>
@@ -1596,35 +1596,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SZPERO</t>
+          <t>Furlan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9472</v>
+        <v>0.7683</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1874</v>
+        <v>0.152</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.193</v>
+        <v>-0.2558</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9472</v>
+        <v>0.7683</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4657</v>
+        <v>0.6848</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4815</v>
+        <v>0.0835</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4657</v>
+        <v>0.6848</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2515</v>
+        <v>0.3845</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4815</v>
+        <v>0.0835</v>
       </c>
       <c r="K26" t="n">
         <v>156</v>
@@ -1633,7 +1633,7 @@
         <v>78</v>
       </c>
       <c r="M26" t="n">
-        <v>0.733</v>
+        <v>0.468</v>
       </c>
       <c r="N26" t="n">
         <v>234</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5941</v>
+        <v>0.6934</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1175</v>
+        <v>0.1372</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3538</v>
+        <v>-0.2899</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5941</v>
+        <v>0.6934</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5941</v>
+        <v>0.6934</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5941</v>
+        <v>0.6934</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.7119</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.7119</v>
       </c>
       <c r="N27" t="n">
         <v>143</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5578</v>
+        <v>0.4679</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1104</v>
+        <v>0.0926</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3703</v>
+        <v>-0.3926</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5578</v>
+        <v>0.4679</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5578</v>
+        <v>0.4679</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5578</v>
+        <v>0.4679</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5578</v>
+        <v>0.4679</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.5578</v>
+        <v>0.4679</v>
       </c>
       <c r="N28" t="n">
         <v>72</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4129</v>
+        <v>0.3163</v>
       </c>
       <c r="C29" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0626</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4362</v>
+        <v>-0.4617</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4129</v>
+        <v>0.3163</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4129</v>
+        <v>0.3163</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4129</v>
+        <v>0.3163</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4235</v>
+        <v>0.3248</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4235</v>
+        <v>0.3248</v>
       </c>
       <c r="N29" t="n">
         <v>200</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3244</v>
+        <v>0.2876</v>
       </c>
       <c r="C30" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0569</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4765</v>
+        <v>-0.4748</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3244</v>
+        <v>0.2876</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3244</v>
+        <v>0.2876</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3244</v>
+        <v>0.2876</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3328</v>
+        <v>0.2953</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3328</v>
+        <v>0.2953</v>
       </c>
       <c r="N30" t="n">
         <v>200</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2565</v>
+        <v>0.2354</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0508</v>
+        <v>0.0466</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5074</v>
+        <v>-0.4986</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2565</v>
+        <v>0.2354</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2565</v>
+        <v>0.2354</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2565</v>
+        <v>0.2354</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2565</v>
+        <v>0.2354</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2565</v>
+        <v>0.2354</v>
       </c>
       <c r="N31" t="n">
         <v>72</v>
@@ -1872,78 +1872,78 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.1516</v>
+        <v>0.1457</v>
       </c>
       <c r="C32" t="n">
-        <v>0.03</v>
+        <v>0.0288</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5552</v>
+        <v>-0.5394</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1516</v>
+        <v>0.1457</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1516</v>
+        <v>0.6992</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.5535</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1516</v>
+        <v>0.6992</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1516</v>
+        <v>0.3926</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.5535</v>
       </c>
       <c r="K32" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1516</v>
+        <v>-0.1609</v>
       </c>
       <c r="N32" t="n">
-        <v>72</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1025</v>
+        <v>0.1236</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0203</v>
+        <v>0.0245</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5775</v>
+        <v>-0.5495</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1025</v>
+        <v>0.1236</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1025</v>
+        <v>0.1236</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1025</v>
+        <v>0.1236</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1025</v>
+        <v>0.1236</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1025</v>
+        <v>0.1236</v>
       </c>
       <c r="N33" t="n">
         <v>72</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0757</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>0.015</v>
+        <v>0.0149</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5897</v>
+        <v>-0.5715</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0757</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6869</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.6112</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6869</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3709</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.6112</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="L34" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2403</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>186</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.1061</v>
+        <v>-0.0707</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.021</v>
+        <v>-0.014</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6725</v>
+        <v>-0.638</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.1061</v>
+        <v>-0.0707</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2606</v>
+        <v>-0.2339</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1545</v>
+        <v>0.1632</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2606</v>
+        <v>-0.2339</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1407</v>
+        <v>-0.1313</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1545</v>
+        <v>0.1632</v>
       </c>
       <c r="K35" t="n">
         <v>54</v>
@@ -2047,7 +2047,7 @@
         <v>132</v>
       </c>
       <c r="M35" t="n">
-        <v>0.01380000000000001</v>
+        <v>0.03190000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>186</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.5813</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1096</v>
+        <v>-0.115</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8763</v>
+        <v>-0.8706</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.5813</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.5813</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.5813</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.5813</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.5813</v>
       </c>
       <c r="N36" t="n">
         <v>131</v>
@@ -2102,32 +2102,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.5794</v>
+        <v>-0.5988</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1146</v>
+        <v>-0.1185</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.888</v>
+        <v>-0.8786</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.5794</v>
+        <v>-0.5988</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.5794</v>
+        <v>-0.5988</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5794</v>
+        <v>-0.5988</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.5794</v>
+        <v>-0.5988</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.5794</v>
+        <v>-0.5988</v>
       </c>
       <c r="N37" t="n">
         <v>131</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3573</v>
+        <v>-1.1915</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2686</v>
+        <v>-0.2357</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2421</v>
+        <v>-1.1486</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3573</v>
+        <v>-1.1915</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8954</v>
+        <v>-0.7427</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.4619</v>
+        <v>-0.4488</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8954</v>
+        <v>-0.7427</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.4835</v>
+        <v>-0.417</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.4619</v>
+        <v>-0.4488</v>
       </c>
       <c r="K38" t="n">
         <v>53</v>
@@ -2185,7 +2185,7 @@
         <v>74</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9454</v>
+        <v>-0.8657999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>127</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4762</v>
+        <v>-1.4755</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2921</v>
+        <v>-0.2919</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2962</v>
+        <v>-1.2779</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4762</v>
+        <v>-1.4755</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4762</v>
+        <v>-1.4755</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4762</v>
+        <v>-1.4755</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4762</v>
+        <v>-1.4755</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4762</v>
+        <v>-1.4755</v>
       </c>
       <c r="N39" t="n">
         <v>72</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.863</v>
+        <v>-1.8531</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3686</v>
+        <v>-0.3667</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4723</v>
+        <v>-1.45</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.863</v>
+        <v>-1.8531</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.863</v>
+        <v>-1.8531</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.863</v>
+        <v>-1.8531</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.911</v>
+        <v>-1.9026</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.911</v>
+        <v>-1.9026</v>
       </c>
       <c r="N40" t="n">
         <v>200</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.3558</v>
+        <v>-2.0936</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4661</v>
+        <v>-0.4142</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6966</v>
+        <v>-1.5595</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.3558</v>
+        <v>-2.0936</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.2243</v>
+        <v>-1.9572</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1315</v>
+        <v>-0.1364</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.2243</v>
+        <v>-1.9572</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.2011</v>
+        <v>-1.0989</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.1315</v>
+        <v>-0.1364</v>
       </c>
       <c r="K41" t="n">
         <v>156</v>
@@ -2323,7 +2323,7 @@
         <v>78</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.3326</v>
+        <v>-1.2353</v>
       </c>
       <c r="N41" t="n">
         <v>234</v>
@@ -2429,10 +2429,10 @@
         <v>1.57</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0184</v>
+        <v>0.9892</v>
       </c>
       <c r="J2" t="n">
-        <v>28.5152</v>
+        <v>27.6976</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.92</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.12</v>
+        <v>-0.1024</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.36</v>
+        <v>-2.8672</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.86</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1868</v>
+        <v>-0.1665</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.2304</v>
+        <v>-4.662</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.85</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1973</v>
+        <v>-0.1769</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.5244</v>
+        <v>-4.9532</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.57</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4595</v>
+        <v>-0.4553</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.866</v>
+        <v>-12.7484</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.45</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0405</v>
+        <v>1.0369</v>
       </c>
       <c r="J7" t="n">
-        <v>29.134</v>
+        <v>29.0332</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9455</v>
+        <v>0.9328</v>
       </c>
       <c r="J8" t="n">
-        <v>26.474</v>
+        <v>26.1184</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.31</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7694</v>
+        <v>0.7439</v>
       </c>
       <c r="J9" t="n">
-        <v>21.5432</v>
+        <v>20.8292</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.98</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1384</v>
+        <v>-0.1114</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.8752</v>
+        <v>-3.1192</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.96</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2089</v>
+        <v>-0.1748</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.8492</v>
+        <v>-4.8944</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.08</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2617</v>
+        <v>0.2189</v>
       </c>
       <c r="J12" t="n">
-        <v>6.8042</v>
+        <v>5.6914</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.88</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1534</v>
+        <v>-0.1374</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.9884</v>
+        <v>-3.5724</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.83</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2061</v>
+        <v>-0.1888</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.3586</v>
+        <v>-4.9088</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.66</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3652</v>
+        <v>-0.3511</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.495200000000001</v>
+        <v>-9.1286</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.6</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.419</v>
+        <v>-0.4092</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.894</v>
+        <v>-10.6392</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.49</v>
       </c>
       <c r="I17" t="n">
-        <v>1.092</v>
+        <v>1.0961</v>
       </c>
       <c r="J17" t="n">
-        <v>28.392</v>
+        <v>28.4986</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.44</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0007</v>
+        <v>0.996</v>
       </c>
       <c r="J18" t="n">
-        <v>26.0182</v>
+        <v>25.896</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.29</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7178</v>
+        <v>0.6949</v>
       </c>
       <c r="J19" t="n">
-        <v>18.6628</v>
+        <v>18.0674</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.24</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6159</v>
+        <v>0.589</v>
       </c>
       <c r="J20" t="n">
-        <v>16.0134</v>
+        <v>15.314</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.13</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3672</v>
+        <v>0.3351</v>
       </c>
       <c r="J21" t="n">
-        <v>9.5472</v>
+        <v>8.7126</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.95</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0389</v>
+        <v>-0.0225</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8169</v>
+        <v>-0.4725</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.71</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3063</v>
+        <v>-0.2935</v>
       </c>
       <c r="J23" t="n">
-        <v>-6.4323</v>
+        <v>-6.1635</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.67</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3414</v>
+        <v>-0.329</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.1694</v>
+        <v>-6.909</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.54</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4557</v>
+        <v>-0.4493</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.569699999999999</v>
+        <v>-9.4353</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.51</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4821</v>
+        <v>-0.4783</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.1241</v>
+        <v>-10.0443</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.86</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3532</v>
+        <v>1.3596</v>
       </c>
       <c r="J27" t="n">
-        <v>28.4172</v>
+        <v>28.5516</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.8</v>
       </c>
       <c r="I28" t="n">
-        <v>1.282</v>
+        <v>1.2842</v>
       </c>
       <c r="J28" t="n">
-        <v>26.922</v>
+        <v>26.9682</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.46</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8628</v>
+        <v>0.8561</v>
       </c>
       <c r="J29" t="n">
-        <v>18.1188</v>
+        <v>17.9781</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.26</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5792</v>
+        <v>0.5772</v>
       </c>
       <c r="J30" t="n">
-        <v>12.1632</v>
+        <v>12.1212</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.23</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5323</v>
+        <v>0.5306</v>
       </c>
       <c r="J31" t="n">
-        <v>11.1783</v>
+        <v>11.1426</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.53</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5948</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>14.2752</v>
+        <v>13.392</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.47</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5139</v>
       </c>
       <c r="J33" t="n">
-        <v>13.1976</v>
+        <v>12.3336</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2478</v>
+        <v>0.2019</v>
       </c>
       <c r="J34" t="n">
-        <v>5.9472</v>
+        <v>4.8456</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0722</v>
+        <v>0.0522</v>
       </c>
       <c r="J35" t="n">
-        <v>1.7328</v>
+        <v>1.2528</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.98</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0606</v>
+        <v>-0.0485</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.4544</v>
+        <v>-1.164</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.19</v>
       </c>
       <c r="I37" t="n">
-        <v>0.357</v>
+        <v>0.3534</v>
       </c>
       <c r="J37" t="n">
-        <v>8.568</v>
+        <v>8.4816</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.89</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1482</v>
+        <v>-0.1311</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.5568</v>
+        <v>-3.1464</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.86</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1796</v>
+        <v>-0.1613</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.3104</v>
+        <v>-3.8712</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.78</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2592</v>
+        <v>-0.2401</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.2208</v>
+        <v>-5.7624</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4161</v>
+        <v>-0.4063</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.9864</v>
+        <v>-9.751200000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.35</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6092</v>
+        <v>0.5807</v>
       </c>
       <c r="J42" t="n">
-        <v>17.6668</v>
+        <v>16.8403</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.12</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2872</v>
+        <v>0.238</v>
       </c>
       <c r="J43" t="n">
-        <v>8.328799999999999</v>
+        <v>6.902</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.93</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1131</v>
+        <v>-0.0951</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.2799</v>
+        <v>-2.7579</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.86</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1927</v>
+        <v>-0.172</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.5883</v>
+        <v>-4.988</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.84</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2137</v>
+        <v>-0.1931</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.1973</v>
+        <v>-5.5999</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.42</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8694</v>
+        <v>0.8544</v>
       </c>
       <c r="J47" t="n">
-        <v>25.2126</v>
+        <v>24.7776</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.19</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.4986</v>
       </c>
       <c r="J48" t="n">
-        <v>14.8944</v>
+        <v>14.4594</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.11</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3501</v>
+        <v>0.3117</v>
       </c>
       <c r="J49" t="n">
-        <v>10.1529</v>
+        <v>9.039300000000001</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.98</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1153</v>
+        <v>-0.0887</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.3437</v>
+        <v>-2.5723</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.76</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6965</v>
+        <v>-0.6647</v>
       </c>
       <c r="J51" t="n">
-        <v>-20.1985</v>
+        <v>-19.2763</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.04</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1172</v>
+        <v>0.1015</v>
       </c>
       <c r="J52" t="n">
-        <v>2.93</v>
+        <v>2.5375</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.95</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0765</v>
+        <v>-0.0641</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.9125</v>
+        <v>-1.6025</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.91</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1263</v>
+        <v>-0.1102</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.1575</v>
+        <v>-2.755</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.89</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1488</v>
+        <v>-0.1315</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.72</v>
+        <v>-3.2875</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.58</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4434</v>
+        <v>-0.4365</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.085</v>
+        <v>-10.9125</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.51</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5756</v>
+        <v>0.5404</v>
       </c>
       <c r="J57" t="n">
-        <v>14.39</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.48</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5534</v>
+        <v>0.5179</v>
       </c>
       <c r="J58" t="n">
-        <v>13.835</v>
+        <v>12.9475</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.4</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4929</v>
+        <v>0.4447</v>
       </c>
       <c r="J59" t="n">
-        <v>12.3225</v>
+        <v>11.1175</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.12</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1913</v>
+        <v>0.1527</v>
       </c>
       <c r="J60" t="n">
-        <v>4.7825</v>
+        <v>3.8175</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.88</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1914</v>
+        <v>-0.1726</v>
       </c>
       <c r="J61" t="n">
-        <v>-4.785</v>
+        <v>-4.315</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.62</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0817</v>
+        <v>1.0731</v>
       </c>
       <c r="J62" t="n">
-        <v>24.8791</v>
+        <v>24.6813</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.47</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8867</v>
+        <v>0.8752</v>
       </c>
       <c r="J63" t="n">
-        <v>20.3941</v>
+        <v>20.1296</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.43</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8334</v>
+        <v>0.8223</v>
       </c>
       <c r="J64" t="n">
-        <v>19.1682</v>
+        <v>18.9129</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.32</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6756</v>
       </c>
       <c r="J65" t="n">
-        <v>15.709</v>
+        <v>15.5388</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.07</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1991</v>
+        <v>0.1691</v>
       </c>
       <c r="J66" t="n">
-        <v>4.5793</v>
+        <v>3.8893</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3162</v>
+        <v>0.2729</v>
       </c>
       <c r="J67" t="n">
-        <v>7.2726</v>
+        <v>6.2767</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.78</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2516</v>
+        <v>-0.2347</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.7868</v>
+        <v>-5.3981</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.76</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.27</v>
+        <v>-0.253</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.21</v>
+        <v>-5.819</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.75</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2792</v>
+        <v>-0.2623</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.4216</v>
+        <v>-6.0329</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.51</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4948</v>
+        <v>-0.493</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.3804</v>
+        <v>-11.339</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.33</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.7329</v>
       </c>
       <c r="J72" t="n">
-        <v>22.455</v>
+        <v>21.987</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.27</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6546</v>
+        <v>0.64</v>
       </c>
       <c r="J73" t="n">
-        <v>19.638</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2379</v>
+        <v>-0.1999</v>
       </c>
       <c r="J74" t="n">
-        <v>-7.137</v>
+        <v>-5.997</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.92</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2955</v>
+        <v>-0.2546</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.865</v>
+        <v>-7.638</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.74</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7306</v>
+        <v>-0.7003</v>
       </c>
       <c r="J76" t="n">
-        <v>-21.918</v>
+        <v>-21.009</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.2</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4229</v>
+        <v>0.3671</v>
       </c>
       <c r="J77" t="n">
-        <v>12.687</v>
+        <v>11.013</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.19</v>
       </c>
       <c r="I78" t="n">
-        <v>0.407</v>
+        <v>0.3509</v>
       </c>
       <c r="J78" t="n">
-        <v>12.21</v>
+        <v>10.527</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.08</v>
       </c>
       <c r="I79" t="n">
-        <v>0.206</v>
+        <v>0.1655</v>
       </c>
       <c r="J79" t="n">
-        <v>6.18</v>
+        <v>4.965</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.95</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0895</v>
+        <v>-0.0731</v>
       </c>
       <c r="J80" t="n">
-        <v>-2.685</v>
+        <v>-2.193</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.8</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2563</v>
+        <v>-0.2367</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.689</v>
+        <v>-7.101</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.01</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1004</v>
+        <v>0.1014</v>
       </c>
       <c r="J82" t="n">
-        <v>2.2088</v>
+        <v>2.2308</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.78</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2423</v>
+        <v>-0.2278</v>
       </c>
       <c r="J83" t="n">
-        <v>-5.3306</v>
+        <v>-5.0116</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.61</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3967</v>
+        <v>-0.3856</v>
       </c>
       <c r="J84" t="n">
-        <v>-8.727399999999999</v>
+        <v>-8.4832</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.61</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3967</v>
+        <v>-0.3856</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.727399999999999</v>
+        <v>-8.4832</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.48</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5113</v>
+        <v>-0.5109</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.2486</v>
+        <v>-11.2398</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.94</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0009</v>
+        <v>0.9424</v>
       </c>
       <c r="J87" t="n">
-        <v>22.0198</v>
+        <v>20.7328</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.61</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7066</v>
+        <v>0.6354</v>
       </c>
       <c r="J88" t="n">
-        <v>15.5452</v>
+        <v>13.9788</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.3</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3993</v>
+        <v>0.3421</v>
       </c>
       <c r="J89" t="n">
-        <v>8.784599999999999</v>
+        <v>7.5262</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.15</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2214</v>
+        <v>0.1795</v>
       </c>
       <c r="J90" t="n">
-        <v>4.8708</v>
+        <v>3.949</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.98</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.0716</v>
+        <v>-0.0607</v>
       </c>
       <c r="J91" t="n">
-        <v>-1.5752</v>
+        <v>-1.3354</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>1.6503</v>
+        <v>1.6937</v>
       </c>
       <c r="J92" t="n">
-        <v>29.7054</v>
+        <v>30.4866</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.83</v>
       </c>
       <c r="I93" t="n">
-        <v>1.454</v>
+        <v>1.4844</v>
       </c>
       <c r="J93" t="n">
-        <v>26.172</v>
+        <v>26.7192</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.58</v>
       </c>
       <c r="I94" t="n">
-        <v>1.1563</v>
+        <v>1.1778</v>
       </c>
       <c r="J94" t="n">
-        <v>20.8134</v>
+        <v>21.2004</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.44</v>
       </c>
       <c r="I95" t="n">
-        <v>0.9644</v>
+        <v>0.9709</v>
       </c>
       <c r="J95" t="n">
-        <v>17.3592</v>
+        <v>17.4762</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.15</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3747</v>
+        <v>0.3403</v>
       </c>
       <c r="J96" t="n">
-        <v>6.7446</v>
+        <v>6.1254</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4187</v>
+        <v>0.4294</v>
       </c>
       <c r="J97" t="n">
-        <v>7.5366</v>
+        <v>7.7292</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.59</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.3975</v>
+        <v>-0.3916</v>
       </c>
       <c r="J98" t="n">
-        <v>-7.155</v>
+        <v>-7.0488</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.47</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4999</v>
+        <v>-0.4986</v>
       </c>
       <c r="J99" t="n">
-        <v>-8.998200000000001</v>
+        <v>-8.9748</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.38</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5797</v>
+        <v>-0.5875</v>
       </c>
       <c r="J100" t="n">
-        <v>-10.4346</v>
+        <v>-10.575</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.27</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.678</v>
+        <v>-0.7028</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.204</v>
+        <v>-12.6504</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.36</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8771</v>
+        <v>0.8577</v>
       </c>
       <c r="J102" t="n">
-        <v>23.6817</v>
+        <v>23.1579</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.33</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8175</v>
+        <v>0.7936</v>
       </c>
       <c r="J103" t="n">
-        <v>22.0725</v>
+        <v>21.4272</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.26</v>
       </c>
       <c r="I104" t="n">
-        <v>0.6746</v>
+        <v>0.6428</v>
       </c>
       <c r="J104" t="n">
-        <v>18.2142</v>
+        <v>17.3556</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.01</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0298</v>
+        <v>0.0199</v>
       </c>
       <c r="J105" t="n">
-        <v>0.8046</v>
+        <v>0.5373</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2642</v>
+        <v>-0.2257</v>
       </c>
       <c r="J106" t="n">
-        <v>-7.1334</v>
+        <v>-6.0939</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.11</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2984</v>
+        <v>0.249</v>
       </c>
       <c r="J107" t="n">
-        <v>8.056800000000001</v>
+        <v>6.723</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.09</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2579</v>
+        <v>0.2114</v>
       </c>
       <c r="J108" t="n">
-        <v>6.9633</v>
+        <v>5.7078</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.89</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1496</v>
+        <v>-0.1319</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.0392</v>
+        <v>-3.5613</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.7</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.337</v>
+        <v>-0.3209</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.099</v>
+        <v>-8.664300000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.65</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3826</v>
+        <v>-0.3698</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.3302</v>
+        <v>-9.9846</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.08</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1766</v>
+        <v>0.1593</v>
       </c>
       <c r="J112" t="n">
-        <v>6.181</v>
+        <v>5.5755</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.05</v>
       </c>
       <c r="I113" t="n">
-        <v>0.125</v>
+        <v>0.1082</v>
       </c>
       <c r="J113" t="n">
-        <v>4.375</v>
+        <v>3.787</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0866</v>
+        <v>0.0718</v>
       </c>
       <c r="J114" t="n">
-        <v>3.031</v>
+        <v>2.513</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.91</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1301</v>
+        <v>-0.1123</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.5535</v>
+        <v>-3.9305</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.6</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4315</v>
+        <v>-0.4239</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.1025</v>
+        <v>-14.8365</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.33</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4498</v>
+        <v>0.3841</v>
       </c>
       <c r="J117" t="n">
-        <v>15.743</v>
+        <v>13.4435</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.21</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3128</v>
+        <v>0.2581</v>
       </c>
       <c r="J118" t="n">
-        <v>10.948</v>
+        <v>9.0335</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.17</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2648</v>
+        <v>0.2155</v>
       </c>
       <c r="J119" t="n">
-        <v>9.268000000000001</v>
+        <v>7.5425</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.11</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1869</v>
+        <v>0.1478</v>
       </c>
       <c r="J120" t="n">
-        <v>6.5415</v>
+        <v>5.173</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.03</v>
       </c>
       <c r="I121" t="n">
-        <v>0.06</v>
+        <v>0.0428</v>
       </c>
       <c r="J121" t="n">
-        <v>2.1</v>
+        <v>1.498</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.36</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8908</v>
+        <v>0.8718</v>
       </c>
       <c r="J122" t="n">
-        <v>25.8332</v>
+        <v>25.2822</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.23</v>
       </c>
       <c r="I123" t="n">
-        <v>0.621</v>
+        <v>0.5851</v>
       </c>
       <c r="J123" t="n">
-        <v>18.009</v>
+        <v>16.9679</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.2</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5553</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J124" t="n">
-        <v>16.1037</v>
+        <v>15.0104</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.02</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0803</v>
+        <v>0.0633</v>
       </c>
       <c r="J125" t="n">
-        <v>2.3287</v>
+        <v>1.8357</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5425</v>
+        <v>-0.5029</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.7325</v>
+        <v>-14.5841</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.45</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8136</v>
+        <v>0.7613</v>
       </c>
       <c r="J127" t="n">
-        <v>23.5944</v>
+        <v>22.0777</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.09</v>
       </c>
       <c r="I128" t="n">
-        <v>0.227</v>
+        <v>0.1839</v>
       </c>
       <c r="J128" t="n">
-        <v>6.583</v>
+        <v>5.3331</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.06</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1653</v>
+        <v>0.1299</v>
       </c>
       <c r="J129" t="n">
-        <v>4.7937</v>
+        <v>3.7671</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1019</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J130" t="n">
-        <v>-2.9551</v>
+        <v>-2.4505</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.64</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4049</v>
+        <v>-0.3956</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.7421</v>
+        <v>-11.4724</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.69</v>
       </c>
       <c r="I132" t="n">
-        <v>1.3282</v>
+        <v>1.349</v>
       </c>
       <c r="J132" t="n">
-        <v>29.2204</v>
+        <v>29.678</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.42</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.9545</v>
       </c>
       <c r="J133" t="n">
-        <v>21.1244</v>
+        <v>20.999</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.27</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6768</v>
+        <v>0.6525</v>
       </c>
       <c r="J134" t="n">
-        <v>14.8896</v>
+        <v>14.355</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.23</v>
       </c>
       <c r="I135" t="n">
-        <v>0.5937</v>
+        <v>0.5662</v>
       </c>
       <c r="J135" t="n">
-        <v>13.0614</v>
+        <v>12.4564</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.02</v>
       </c>
       <c r="I136" t="n">
-        <v>0.0465</v>
+        <v>0.0294</v>
       </c>
       <c r="J136" t="n">
-        <v>1.023</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.2</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4895</v>
+        <v>0.4388</v>
       </c>
       <c r="J137" t="n">
-        <v>10.769</v>
+        <v>9.653600000000001</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2982</v>
+        <v>0.2519</v>
       </c>
       <c r="J138" t="n">
-        <v>6.5604</v>
+        <v>5.5418</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.109</v>
+        <v>-0.0946</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.398</v>
+        <v>-2.0812</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.47</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.534</v>
+        <v>-0.5381</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.748</v>
+        <v>-11.8382</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.44</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5596</v>
+        <v>-0.5676</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.3112</v>
+        <v>-12.4872</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.59</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1974</v>
+        <v>1.2127</v>
       </c>
       <c r="J142" t="n">
-        <v>28.7376</v>
+        <v>29.1048</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.54</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1321</v>
+        <v>1.1458</v>
       </c>
       <c r="J143" t="n">
-        <v>27.1704</v>
+        <v>27.4992</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.5</v>
       </c>
       <c r="I144" t="n">
-        <v>1.0792</v>
+        <v>1.0905</v>
       </c>
       <c r="J144" t="n">
-        <v>25.9008</v>
+        <v>26.172</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.08</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2337</v>
+        <v>0.2033</v>
       </c>
       <c r="J145" t="n">
-        <v>5.6088</v>
+        <v>4.8792</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.99</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.1167</v>
+        <v>-0.0978</v>
       </c>
       <c r="J146" t="n">
-        <v>-2.8008</v>
+        <v>-2.3472</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.12</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3309</v>
+        <v>0.2815</v>
       </c>
       <c r="J147" t="n">
-        <v>7.9416</v>
+        <v>6.756</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.88</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1575</v>
+        <v>-0.1406</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.78</v>
+        <v>-3.3744</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.86</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1787</v>
+        <v>-0.1609</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.2888</v>
+        <v>-3.8616</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.83</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2085</v>
+        <v>-0.19</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.004</v>
+        <v>-4.56</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.55</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4671</v>
+        <v>-0.4626</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.2104</v>
+        <v>-11.1024</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.61</v>
       </c>
       <c r="I152" t="n">
-        <v>1.2138</v>
+        <v>1.2305</v>
       </c>
       <c r="J152" t="n">
-        <v>26.7036</v>
+        <v>27.071</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.54</v>
       </c>
       <c r="I153" t="n">
-        <v>1.1239</v>
+        <v>1.1387</v>
       </c>
       <c r="J153" t="n">
-        <v>24.7258</v>
+        <v>25.0514</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.46</v>
       </c>
       <c r="I154" t="n">
-        <v>1.0151</v>
+        <v>1.0205</v>
       </c>
       <c r="J154" t="n">
-        <v>22.3322</v>
+        <v>22.451</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.45</v>
       </c>
       <c r="I155" t="n">
-        <v>0.9998</v>
+        <v>1.0031</v>
       </c>
       <c r="J155" t="n">
-        <v>21.9956</v>
+        <v>22.0682</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.93</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3288</v>
+        <v>-0.2944</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.2336</v>
+        <v>-6.4768</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.19</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4765</v>
+        <v>0.4269</v>
       </c>
       <c r="J157" t="n">
-        <v>10.483</v>
+        <v>9.3918</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.96</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0543</v>
+        <v>-0.0436</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.1946</v>
+        <v>-0.9592000000000001</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.78</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2542</v>
+        <v>-0.2362</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.5924</v>
+        <v>-5.1964</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.7</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3291</v>
+        <v>-0.3129</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.2402</v>
+        <v>-6.8838</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.44</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5585</v>
+        <v>-0.5661</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.287</v>
+        <v>-12.4542</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.29</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5985</v>
+        <v>0.5416</v>
       </c>
       <c r="J162" t="n">
-        <v>17.955</v>
+        <v>16.248</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.17</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3954</v>
+        <v>0.3398</v>
       </c>
       <c r="J163" t="n">
-        <v>11.862</v>
+        <v>10.194</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.96</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0693</v>
+        <v>-0.0565</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.079</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.95</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.0684</v>
       </c>
       <c r="J165" t="n">
-        <v>-2.478</v>
+        <v>-2.052</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.35</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6433</v>
+        <v>-0.6677</v>
       </c>
       <c r="J166" t="n">
-        <v>-19.299</v>
+        <v>-20.031</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.4</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9546</v>
+        <v>0.9437</v>
       </c>
       <c r="J167" t="n">
-        <v>28.638</v>
+        <v>28.311</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.39</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9361</v>
+        <v>0.9226</v>
       </c>
       <c r="J168" t="n">
-        <v>28.083</v>
+        <v>27.678</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.34</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8384</v>
+        <v>0.8159</v>
       </c>
       <c r="J169" t="n">
-        <v>25.152</v>
+        <v>24.477</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.95</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.233</v>
+        <v>-0.1962</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.99</v>
+        <v>-5.886</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.8</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6213</v>
+        <v>-0.5866</v>
       </c>
       <c r="J171" t="n">
-        <v>-18.639</v>
+        <v>-17.598</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.4</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5343</v>
+        <v>0.4647</v>
       </c>
       <c r="J172" t="n">
-        <v>15.4947</v>
+        <v>13.4763</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.34</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4685</v>
+        <v>0.4014</v>
       </c>
       <c r="J173" t="n">
-        <v>13.5865</v>
+        <v>11.6406</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3302</v>
+        <v>0.2726</v>
       </c>
       <c r="J174" t="n">
-        <v>9.575799999999999</v>
+        <v>7.9054</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.91</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1452</v>
+        <v>-0.1255</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.2108</v>
+        <v>-3.6395</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.71</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.348</v>
+        <v>-0.3343</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.092</v>
+        <v>-9.694699999999999</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.17</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3061</v>
+        <v>0.2945</v>
       </c>
       <c r="J177" t="n">
-        <v>8.876899999999999</v>
+        <v>8.5405</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.11</v>
       </c>
       <c r="I178" t="n">
-        <v>0.219</v>
+        <v>0.2026</v>
       </c>
       <c r="J178" t="n">
-        <v>6.351</v>
+        <v>5.8754</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.01</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0376</v>
+        <v>0.0282</v>
       </c>
       <c r="J179" t="n">
-        <v>1.0904</v>
+        <v>0.8178</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.76</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2879</v>
+        <v>-0.2692</v>
       </c>
       <c r="J180" t="n">
-        <v>-8.3491</v>
+        <v>-7.8068</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.76</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2879</v>
+        <v>-0.2692</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.3491</v>
+        <v>-7.8068</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.3</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.5373</v>
       </c>
       <c r="J182" t="n">
-        <v>17.889</v>
+        <v>16.119</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.26</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5323</v>
+        <v>0.473</v>
       </c>
       <c r="J183" t="n">
-        <v>15.969</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.02</v>
       </c>
       <c r="I184" t="n">
-        <v>0.073</v>
+        <v>0.0522</v>
       </c>
       <c r="J184" t="n">
-        <v>2.19</v>
+        <v>1.566</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.92</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.124</v>
+        <v>-0.1054</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.72</v>
+        <v>-3.162</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.52</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5063</v>
+        <v>-0.5089</v>
       </c>
       <c r="J186" t="n">
-        <v>-15.189</v>
+        <v>-15.267</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.27</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7221</v>
+        <v>0.6899</v>
       </c>
       <c r="J187" t="n">
-        <v>21.663</v>
+        <v>20.697</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.27</v>
       </c>
       <c r="I188" t="n">
-        <v>0.7221</v>
+        <v>0.6899</v>
       </c>
       <c r="J188" t="n">
-        <v>21.663</v>
+        <v>20.697</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.16</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4759</v>
+        <v>0.4348</v>
       </c>
       <c r="J189" t="n">
-        <v>14.277</v>
+        <v>13.044</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.83</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.531</v>
+        <v>-0.4901</v>
       </c>
       <c r="J190" t="n">
-        <v>-15.93</v>
+        <v>-14.703</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5782</v>
+        <v>-0.539</v>
       </c>
       <c r="J191" t="n">
-        <v>-17.346</v>
+        <v>-16.17</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.39</v>
       </c>
       <c r="I192" t="n">
-        <v>0.9262</v>
+        <v>0.9124</v>
       </c>
       <c r="J192" t="n">
-        <v>22.2288</v>
+        <v>21.8976</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.36</v>
       </c>
       <c r="I193" t="n">
-        <v>0.8685</v>
+        <v>0.8495</v>
       </c>
       <c r="J193" t="n">
-        <v>20.844</v>
+        <v>20.388</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.13</v>
       </c>
       <c r="I194" t="n">
-        <v>0.383</v>
+        <v>0.3494</v>
       </c>
       <c r="J194" t="n">
-        <v>9.192</v>
+        <v>8.3856</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.11</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3331</v>
+        <v>0.3002</v>
       </c>
       <c r="J195" t="n">
-        <v>7.9944</v>
+        <v>7.2048</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.1</v>
       </c>
       <c r="I196" t="n">
-        <v>0.3073</v>
+        <v>0.275</v>
       </c>
       <c r="J196" t="n">
-        <v>7.3752</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I197" t="n">
-        <v>0.446</v>
+        <v>0.3908</v>
       </c>
       <c r="J197" t="n">
-        <v>10.704</v>
+        <v>9.379200000000001</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0607</v>
+        <v>0.0422</v>
       </c>
       <c r="J198" t="n">
-        <v>1.4568</v>
+        <v>1.0128</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.85</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.192</v>
+        <v>-0.1726</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.608</v>
+        <v>-4.1424</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.77</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2716</v>
+        <v>-0.2526</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.5184</v>
+        <v>-6.0624</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.65</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3832</v>
+        <v>-0.3705</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.1968</v>
+        <v>-8.891999999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.4</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7601</v>
+        <v>0.7078</v>
       </c>
       <c r="J202" t="n">
-        <v>21.2828</v>
+        <v>19.8184</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.09</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2375</v>
+        <v>0.1921</v>
       </c>
       <c r="J203" t="n">
-        <v>6.65</v>
+        <v>5.3788</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.93</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1095</v>
+        <v>-0.0922</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.066</v>
+        <v>-2.5816</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.8</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.25</v>
+        <v>-0.2301</v>
       </c>
       <c r="J205" t="n">
-        <v>-7</v>
+        <v>-6.4428</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3907</v>
+        <v>-0.3794</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.9396</v>
+        <v>-10.6232</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.36</v>
       </c>
       <c r="I207" t="n">
-        <v>0.8937</v>
+        <v>0.8749</v>
       </c>
       <c r="J207" t="n">
-        <v>25.0236</v>
+        <v>24.4972</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.12</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3719</v>
+        <v>0.3343</v>
       </c>
       <c r="J208" t="n">
-        <v>10.4132</v>
+        <v>9.3604</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.07</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2421</v>
+        <v>0.2099</v>
       </c>
       <c r="J209" t="n">
-        <v>6.7788</v>
+        <v>5.8772</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.06</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2134</v>
+        <v>0.1831</v>
       </c>
       <c r="J210" t="n">
-        <v>5.9752</v>
+        <v>5.1268</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.98</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1201</v>
+        <v>-0.093</v>
       </c>
       <c r="J211" t="n">
-        <v>-3.3628</v>
+        <v>-2.604</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.37</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6892</v>
+        <v>0.6309</v>
       </c>
       <c r="J212" t="n">
-        <v>17.9192</v>
+        <v>16.4034</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.27</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5354</v>
+        <v>0.4757</v>
       </c>
       <c r="J213" t="n">
-        <v>13.9204</v>
+        <v>12.3682</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.12</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2812</v>
+        <v>0.2333</v>
       </c>
       <c r="J214" t="n">
-        <v>7.3112</v>
+        <v>6.0658</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.97</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0625</v>
+        <v>-0.0489</v>
       </c>
       <c r="J215" t="n">
-        <v>-1.625</v>
+        <v>-1.2714</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4762</v>
+        <v>-0.4755</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.3812</v>
+        <v>-12.363</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.39</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9536</v>
+        <v>0.9424</v>
       </c>
       <c r="J217" t="n">
-        <v>24.7936</v>
+        <v>24.5024</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.28</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7313</v>
+        <v>0.7002</v>
       </c>
       <c r="J218" t="n">
-        <v>19.0138</v>
+        <v>18.2052</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.2</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5584</v>
+        <v>0.5201</v>
       </c>
       <c r="J219" t="n">
-        <v>14.5184</v>
+        <v>13.5226</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.91</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3371</v>
+        <v>-0.295</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.7646</v>
+        <v>-7.67</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.78</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6554</v>
+        <v>-0.6213</v>
       </c>
       <c r="J221" t="n">
-        <v>-17.0404</v>
+        <v>-16.1538</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.59</v>
       </c>
       <c r="I222" t="n">
-        <v>1.2126</v>
+        <v>1.2279</v>
       </c>
       <c r="J222" t="n">
-        <v>30.315</v>
+        <v>30.6975</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.38</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.8835</v>
       </c>
       <c r="J223" t="n">
-        <v>22.4675</v>
+        <v>22.0875</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.23</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6025</v>
+        <v>0.5727</v>
       </c>
       <c r="J224" t="n">
-        <v>15.0625</v>
+        <v>14.3175</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.19</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5162</v>
+        <v>0.4845</v>
       </c>
       <c r="J225" t="n">
-        <v>12.905</v>
+        <v>12.1125</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.91</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3634</v>
+        <v>-0.324</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.085000000000001</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.2</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4736</v>
+        <v>0.4197</v>
       </c>
       <c r="J227" t="n">
-        <v>11.84</v>
+        <v>10.4925</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.95</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0756</v>
+        <v>-0.0633</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.89</v>
+        <v>-1.5825</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.91</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1255</v>
+        <v>-0.1097</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.1375</v>
+        <v>-2.7425</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.64</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3893</v>
+        <v>-0.3771</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.7325</v>
+        <v>-9.4275</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.63</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3983</v>
+        <v>-0.3868</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.9575</v>
+        <v>-9.67</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.28</v>
       </c>
       <c r="I232" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5058</v>
       </c>
       <c r="J232" t="n">
-        <v>16.95</v>
+        <v>15.174</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.12</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2905</v>
+        <v>0.2407</v>
       </c>
       <c r="J233" t="n">
-        <v>8.715</v>
+        <v>7.221</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.97</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0583</v>
+        <v>-0.0457</v>
       </c>
       <c r="J234" t="n">
-        <v>-1.749</v>
+        <v>-1.371</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.89</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1584</v>
+        <v>-0.1384</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.752</v>
+        <v>-4.152</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.75</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3011</v>
+        <v>-0.2833</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.032999999999999</v>
+        <v>-8.499000000000001</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.47</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0747</v>
+        <v>1.0837</v>
       </c>
       <c r="J237" t="n">
-        <v>32.241</v>
+        <v>32.511</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.38</v>
       </c>
       <c r="I238" t="n">
-        <v>0.925</v>
+        <v>0.9097</v>
       </c>
       <c r="J238" t="n">
-        <v>27.75</v>
+        <v>27.291</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.16</v>
       </c>
       <c r="I239" t="n">
-        <v>0.4625</v>
+        <v>0.4251</v>
       </c>
       <c r="J239" t="n">
-        <v>13.875</v>
+        <v>12.753</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.87</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.448</v>
+        <v>-0.4063</v>
       </c>
       <c r="J240" t="n">
-        <v>-13.44</v>
+        <v>-12.189</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.85</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4976</v>
+        <v>-0.4569</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.928</v>
+        <v>-13.707</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.14</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3167</v>
+        <v>0.2661</v>
       </c>
       <c r="J242" t="n">
-        <v>13.3014</v>
+        <v>11.1762</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.12</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2803</v>
+        <v>0.2327</v>
       </c>
       <c r="J243" t="n">
-        <v>11.7726</v>
+        <v>9.773400000000001</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.08</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2038</v>
+        <v>0.1642</v>
       </c>
       <c r="J244" t="n">
-        <v>8.5596</v>
+        <v>6.8964</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.05</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1414</v>
+        <v>0.1104</v>
       </c>
       <c r="J245" t="n">
-        <v>5.9388</v>
+        <v>4.6368</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.93</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1168</v>
+        <v>-0.0983</v>
       </c>
       <c r="J246" t="n">
-        <v>-4.9056</v>
+        <v>-4.1286</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.37</v>
       </c>
       <c r="I247" t="n">
-        <v>0.9355</v>
+        <v>0.9226</v>
       </c>
       <c r="J247" t="n">
-        <v>39.291</v>
+        <v>38.7492</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.22</v>
       </c>
       <c r="I248" t="n">
-        <v>0.618</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="J248" t="n">
-        <v>25.956</v>
+        <v>24.3642</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2399</v>
+        <v>-0.2016</v>
       </c>
       <c r="J249" t="n">
-        <v>-10.0758</v>
+        <v>-8.4672</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.91</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.325</v>
+        <v>-0.283</v>
       </c>
       <c r="J250" t="n">
-        <v>-13.65</v>
+        <v>-11.886</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5746</v>
+        <v>-0.535</v>
       </c>
       <c r="J251" t="n">
-        <v>-24.1332</v>
+        <v>-22.47</v>
       </c>
     </row>
   </sheetData>
